--- a/memo/Partner_Discussion_Worksheet.xlsx
+++ b/memo/Partner_Discussion_Worksheet.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bigspacey/Downloads/files/clinic-booking/memo/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B19CB80-A3D1-044D-A91B-895DAD6437E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -14,12 +20,25 @@
     <sheet name="Projection" sheetId="5" r:id="rId5"/>
     <sheet name="Profit Split" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="328">
   <si>
     <t>Partner Discussion Worksheet</t>
   </si>
@@ -985,16 +1004,33 @@
   </si>
   <si>
     <t>Worst position vs cap</t>
+  </si>
+  <si>
+    <t>Kanan Digital Sdn Bhd</t>
+  </si>
+  <si>
+    <t>100 usd per month</t>
+  </si>
+  <si>
+    <t>- Patient booking system</t>
+  </si>
+  <si>
+    <t>- Duty calendar + related features</t>
+  </si>
+  <si>
+    <t>Premium</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="#,##0;-#,##0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="#,##0;\-#,##0"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -1203,7 +1239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1211,17 +1247,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1235,38 +1265,85 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="10" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <font>
         <b/>
         <color rgb="FFC0392B"/>
       </font>
-      <numFmt numFmtId="166" formatCode="#,##0;-#,##0"/>
+      <numFmt numFmtId="165" formatCode="#,##0;\-#,##0"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFE7E5E4"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFE7E5E4"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFE7E5E4"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFE7E5E4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC0392B"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0;\-#,##0"/>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFFFF"/>
@@ -1291,13 +1368,21 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1335,7 +1420,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1369,6 +1454,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1403,9 +1489,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1578,16 +1665,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF0D9488"/>
   </sheetPr>
-  <dimension ref="A2:C25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="B2:C25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" customWidth="1"/>
-    <col min="2" max="2" width="36.7109375" customWidth="1"/>
-    <col min="3" max="3" width="80.7109375" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" customWidth="1"/>
+    <col min="2" max="2" width="36.6640625" customWidth="1"/>
+    <col min="3" max="3" width="80.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="38" customHeight="1">
@@ -1595,1797 +1682,1825 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:3">
+    <row r="3" spans="2:3" ht="16">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="22" customHeight="1">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="16"/>
     </row>
     <row r="6" spans="2:3" ht="64" customHeight="1">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="4"/>
+      <c r="C6" s="17"/>
     </row>
     <row r="8" spans="2:3" ht="22" customHeight="1">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="3"/>
+      <c r="C8" s="16"/>
     </row>
     <row r="9" spans="2:3" ht="22" customHeight="1">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="22" customHeight="1">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="22" customHeight="1">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="22" customHeight="1">
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="13" spans="2:3" ht="22" customHeight="1">
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="22" customHeight="1">
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="22" customHeight="1">
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="3"/>
+      <c r="C16" s="16"/>
     </row>
     <row r="17" spans="2:3" ht="20" customHeight="1">
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="4"/>
+      <c r="C17" s="17"/>
     </row>
     <row r="18" spans="2:3" ht="20" customHeight="1">
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="4"/>
+      <c r="C18" s="17"/>
     </row>
     <row r="19" spans="2:3" ht="20" customHeight="1">
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="4"/>
+      <c r="C19" s="17"/>
     </row>
     <row r="20" spans="2:3" ht="20" customHeight="1">
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="4"/>
+      <c r="C20" s="17"/>
     </row>
     <row r="21" spans="2:3" ht="20" customHeight="1">
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="4"/>
+      <c r="C21" s="17"/>
     </row>
     <row r="22" spans="2:3" ht="20" customHeight="1">
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="4"/>
+      <c r="C22" s="17"/>
     </row>
     <row r="24" spans="2:3" ht="22" customHeight="1">
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="3"/>
+      <c r="C24" s="16"/>
     </row>
     <row r="25" spans="2:3" ht="48" customHeight="1">
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="4"/>
+      <c r="C25" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF0F766E"/>
   </sheetPr>
-  <dimension ref="B2:D96"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="B2:F96"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" customWidth="1"/>
-    <col min="2" max="2" width="6.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
-    <col min="4" max="4" width="70.7109375" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" customWidth="1"/>
+    <col min="2" max="2" width="6.6640625" customWidth="1"/>
+    <col min="3" max="3" width="50.6640625" customWidth="1"/>
+    <col min="4" max="4" width="70.6640625" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" style="21"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="32" customHeight="1">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:6" ht="32" customHeight="1">
+      <c r="B2" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="2:4" ht="44" customHeight="1">
-      <c r="B3" s="2" t="s">
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+    </row>
+    <row r="3" spans="2:6" ht="44" customHeight="1">
+      <c r="B3" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="5" spans="2:4" ht="24" customHeight="1">
-      <c r="B5" s="6" t="s">
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+    </row>
+    <row r="5" spans="2:6" ht="24" customHeight="1">
+      <c r="B5" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-    </row>
-    <row r="6" spans="2:4" ht="22" customHeight="1">
-      <c r="B6" s="7" t="s">
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+    </row>
+    <row r="6" spans="2:6" ht="22" customHeight="1">
+      <c r="B6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="34" customHeight="1">
-      <c r="B7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="9" t="s">
+    <row r="7" spans="2:6" ht="34" customHeight="1">
+      <c r="B7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="7" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="8" spans="2:4" ht="34" customHeight="1">
-      <c r="B8" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="10" t="s">
+      <c r="F7" s="21" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="34" customHeight="1">
+      <c r="B8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="34" customHeight="1">
-      <c r="B9" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="9" t="s">
+    <row r="9" spans="2:6" ht="34" customHeight="1">
+      <c r="B9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="7" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="34" customHeight="1">
-      <c r="B10" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="10" t="s">
+    <row r="10" spans="2:6" ht="34" customHeight="1">
+      <c r="B10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="34" customHeight="1">
-      <c r="B11" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="9" t="s">
+    <row r="11" spans="2:6" ht="34" customHeight="1">
+      <c r="B11" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="7" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="34" customHeight="1">
-      <c r="B12" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="10" t="s">
+    <row r="12" spans="2:6" ht="34" customHeight="1">
+      <c r="B12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="34" customHeight="1">
-      <c r="B13" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="9" t="s">
+    <row r="13" spans="2:6" ht="34" customHeight="1">
+      <c r="B13" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="34" customHeight="1">
-      <c r="B14" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="10" t="s">
+    <row r="14" spans="2:6" ht="34" customHeight="1">
+      <c r="B14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="34" customHeight="1">
-      <c r="B15" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="9" t="s">
+    <row r="15" spans="2:6" ht="34" customHeight="1">
+      <c r="B15" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="2:4" ht="34" customHeight="1">
-      <c r="B16" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="10" t="s">
+    <row r="16" spans="2:6" ht="34" customHeight="1">
+      <c r="B16" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="8" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="24" customHeight="1">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
     </row>
     <row r="19" spans="2:4" ht="22" customHeight="1">
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="34" customHeight="1">
-      <c r="B20" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="9" t="s">
+      <c r="B20" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="7" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="34" customHeight="1">
-      <c r="B21" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="10" t="s">
+      <c r="B21" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="8" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="22" spans="2:4" ht="34" customHeight="1">
-      <c r="B22" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="9" t="s">
+      <c r="B22" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="7" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="23" spans="2:4" ht="34" customHeight="1">
-      <c r="B23" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="10" t="s">
+      <c r="B23" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="8" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="24" spans="2:4" ht="34" customHeight="1">
-      <c r="B24" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="9" t="s">
+      <c r="B24" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="7" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="34" customHeight="1">
-      <c r="B25" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" s="10" t="s">
+      <c r="B25" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="8" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="34" customHeight="1">
-      <c r="B26" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="9" t="s">
+      <c r="B26" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="7" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="27" spans="2:4" ht="34" customHeight="1">
-      <c r="B27" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" s="10" t="s">
+      <c r="B27" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="8" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="28" spans="2:4" ht="34" customHeight="1">
-      <c r="B28" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" s="9" t="s">
+      <c r="B28" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="7" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="30" spans="2:4" ht="24" customHeight="1">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
     </row>
     <row r="31" spans="2:4" ht="22" customHeight="1">
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="32" spans="2:4" ht="34" customHeight="1">
-      <c r="B32" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" s="9" t="s">
+      <c r="B32" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="D32" s="7" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="33" spans="2:4" ht="34" customHeight="1">
-      <c r="B33" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C33" s="10" t="s">
+      <c r="B33" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="8" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="34" spans="2:4" ht="34" customHeight="1">
-      <c r="B34" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" s="9" t="s">
+      <c r="B34" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="D34" s="7" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="35" spans="2:4" ht="34" customHeight="1">
-      <c r="B35" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" s="10" t="s">
+      <c r="B35" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="8" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="36" spans="2:4" ht="34" customHeight="1">
-      <c r="B36" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C36" s="9" t="s">
+      <c r="B36" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="D36" s="7" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="37" spans="2:4" ht="34" customHeight="1">
-      <c r="B37" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C37" s="10" t="s">
+      <c r="B37" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="D37" s="8" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="38" spans="2:4" ht="34" customHeight="1">
-      <c r="B38" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" s="9" t="s">
+      <c r="B38" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="D38" s="9" t="s">
+      <c r="D38" s="7" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="39" spans="2:4" ht="34" customHeight="1">
-      <c r="B39" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C39" s="10" t="s">
+      <c r="B39" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="8" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="40" spans="2:4" ht="34" customHeight="1">
-      <c r="B40" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C40" s="9" t="s">
+      <c r="B40" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D40" s="9" t="s">
+      <c r="D40" s="7" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="41" spans="2:4" ht="34" customHeight="1">
-      <c r="B41" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C41" s="10" t="s">
+      <c r="B41" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" s="8" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="43" spans="2:4" ht="24" customHeight="1">
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20"/>
     </row>
     <row r="44" spans="2:4" ht="22" customHeight="1">
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D44" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="45" spans="2:4" ht="34" customHeight="1">
-      <c r="B45" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C45" s="9" t="s">
+      <c r="B45" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C45" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D45" s="7" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="46" spans="2:4" ht="34" customHeight="1">
-      <c r="B46" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C46" s="10" t="s">
+      <c r="B46" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C46" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="D46" s="8" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="47" spans="2:4" ht="34" customHeight="1">
-      <c r="B47" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C47" s="9" t="s">
+      <c r="B47" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C47" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D47" s="9" t="s">
+      <c r="D47" s="7" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="48" spans="2:4" ht="34" customHeight="1">
-      <c r="B48" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C48" s="10" t="s">
+      <c r="B48" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C48" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D48" s="10" t="s">
+      <c r="D48" s="8" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="49" spans="2:4" ht="34" customHeight="1">
-      <c r="B49" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C49" s="9" t="s">
+      <c r="B49" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D49" s="9" t="s">
+      <c r="D49" s="7" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="50" spans="2:4" ht="34" customHeight="1">
-      <c r="B50" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C50" s="10" t="s">
+      <c r="B50" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="D50" s="8" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="51" spans="2:4" ht="34" customHeight="1">
-      <c r="B51" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C51" s="9" t="s">
+      <c r="B51" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C51" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D51" s="9" t="s">
+      <c r="D51" s="7" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="52" spans="2:4" ht="34" customHeight="1">
-      <c r="B52" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C52" s="10" t="s">
+      <c r="B52" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="D52" s="10" t="s">
+      <c r="D52" s="8" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="54" spans="2:4" ht="24" customHeight="1">
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="20"/>
     </row>
     <row r="55" spans="2:4" ht="22" customHeight="1">
-      <c r="B55" s="7" t="s">
+      <c r="B55" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D55" s="7" t="s">
+      <c r="D55" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="56" spans="2:4" ht="34" customHeight="1">
-      <c r="B56" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C56" s="9" t="s">
+      <c r="B56" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C56" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="D56" s="9" t="s">
+      <c r="D56" s="7" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="57" spans="2:4" ht="34" customHeight="1">
-      <c r="B57" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C57" s="10" t="s">
+      <c r="B57" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C57" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="D57" s="10" t="s">
+      <c r="D57" s="8" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="58" spans="2:4" ht="34" customHeight="1">
-      <c r="B58" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C58" s="9" t="s">
+      <c r="B58" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C58" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="D58" s="9" t="s">
+      <c r="D58" s="7" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="59" spans="2:4" ht="34" customHeight="1">
-      <c r="B59" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C59" s="10" t="s">
+      <c r="B59" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C59" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="D59" s="10" t="s">
+      <c r="D59" s="8" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="60" spans="2:4" ht="34" customHeight="1">
-      <c r="B60" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C60" s="9" t="s">
+      <c r="B60" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C60" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D60" s="9" t="s">
+      <c r="D60" s="7" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="61" spans="2:4" ht="34" customHeight="1">
-      <c r="B61" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C61" s="10" t="s">
+      <c r="B61" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C61" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="D61" s="10" t="s">
+      <c r="D61" s="8" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="62" spans="2:4" ht="34" customHeight="1">
-      <c r="B62" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C62" s="9" t="s">
+      <c r="B62" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C62" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D62" s="9" t="s">
+      <c r="D62" s="7" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="63" spans="2:4" ht="34" customHeight="1">
-      <c r="B63" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C63" s="10" t="s">
+      <c r="B63" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C63" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="D63" s="10" t="s">
+      <c r="D63" s="8" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="65" spans="2:4" ht="24" customHeight="1">
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
+      <c r="C65" s="20"/>
+      <c r="D65" s="20"/>
     </row>
     <row r="66" spans="2:4" ht="22" customHeight="1">
-      <c r="B66" s="7" t="s">
+      <c r="B66" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="C66" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="D66" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="67" spans="2:4" ht="34" customHeight="1">
-      <c r="B67" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C67" s="9" t="s">
+      <c r="B67" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C67" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="D67" s="9" t="s">
+      <c r="D67" s="7" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="68" spans="2:4" ht="34" customHeight="1">
-      <c r="B68" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C68" s="10" t="s">
+      <c r="B68" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C68" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="D68" s="10" t="s">
+      <c r="D68" s="8" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="69" spans="2:4" ht="34" customHeight="1">
-      <c r="B69" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C69" s="9" t="s">
+      <c r="B69" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C69" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="D69" s="9" t="s">
+      <c r="D69" s="7" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="70" spans="2:4" ht="34" customHeight="1">
-      <c r="B70" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C70" s="10" t="s">
+      <c r="B70" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C70" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D70" s="10" t="s">
+      <c r="D70" s="8" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="71" spans="2:4" ht="34" customHeight="1">
-      <c r="B71" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C71" s="9" t="s">
+      <c r="B71" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C71" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="D71" s="9" t="s">
+      <c r="D71" s="7" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="72" spans="2:4" ht="34" customHeight="1">
-      <c r="B72" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C72" s="10" t="s">
+      <c r="B72" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C72" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="D72" s="10" t="s">
+      <c r="D72" s="8" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="73" spans="2:4" ht="34" customHeight="1">
-      <c r="B73" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C73" s="9" t="s">
+      <c r="B73" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C73" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="D73" s="9" t="s">
+      <c r="D73" s="7" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="74" spans="2:4" ht="34" customHeight="1">
-      <c r="B74" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C74" s="10" t="s">
+      <c r="B74" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C74" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="D74" s="10" t="s">
+      <c r="D74" s="8" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="75" spans="2:4" ht="34" customHeight="1">
-      <c r="B75" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C75" s="9" t="s">
+      <c r="B75" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C75" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="D75" s="9" t="s">
+      <c r="D75" s="7" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="77" spans="2:4" ht="24" customHeight="1">
-      <c r="B77" s="6" t="s">
+      <c r="B77" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="C77" s="6"/>
-      <c r="D77" s="6"/>
+      <c r="C77" s="20"/>
+      <c r="D77" s="20"/>
     </row>
     <row r="78" spans="2:4" ht="22" customHeight="1">
-      <c r="B78" s="7" t="s">
+      <c r="B78" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C78" s="7" t="s">
+      <c r="C78" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D78" s="7" t="s">
+      <c r="D78" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="79" spans="2:4" ht="34" customHeight="1">
-      <c r="B79" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C79" s="9" t="s">
+      <c r="B79" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C79" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D79" s="9" t="s">
+      <c r="D79" s="7" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="80" spans="2:4" ht="34" customHeight="1">
-      <c r="B80" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C80" s="10" t="s">
+      <c r="B80" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C80" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="D80" s="10" t="s">
+      <c r="D80" s="8" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="81" spans="2:4" ht="34" customHeight="1">
-      <c r="B81" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C81" s="9" t="s">
+      <c r="B81" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C81" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="D81" s="9" t="s">
+      <c r="D81" s="7" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="82" spans="2:4" ht="34" customHeight="1">
-      <c r="B82" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C82" s="10" t="s">
+      <c r="B82" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C82" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="D82" s="10" t="s">
+      <c r="D82" s="8" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="83" spans="2:4" ht="34" customHeight="1">
-      <c r="B83" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C83" s="9" t="s">
+      <c r="B83" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C83" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="D83" s="9" t="s">
+      <c r="D83" s="7" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="84" spans="2:4" ht="34" customHeight="1">
-      <c r="B84" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C84" s="10" t="s">
+      <c r="B84" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C84" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="D84" s="10" t="s">
+      <c r="D84" s="8" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="85" spans="2:4" ht="34" customHeight="1">
-      <c r="B85" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C85" s="9" t="s">
+      <c r="B85" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C85" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="D85" s="9" t="s">
+      <c r="D85" s="7" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="86" spans="2:4" ht="34" customHeight="1">
-      <c r="B86" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C86" s="10" t="s">
+      <c r="B86" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C86" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="D86" s="10" t="s">
+      <c r="D86" s="8" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="88" spans="2:4" ht="24" customHeight="1">
-      <c r="B88" s="6" t="s">
+      <c r="B88" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="C88" s="6"/>
-      <c r="D88" s="6"/>
+      <c r="C88" s="20"/>
+      <c r="D88" s="20"/>
     </row>
     <row r="89" spans="2:4" ht="22" customHeight="1">
-      <c r="B89" s="7" t="s">
+      <c r="B89" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C89" s="7" t="s">
+      <c r="C89" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D89" s="7" t="s">
+      <c r="D89" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="90" spans="2:4" ht="34" customHeight="1">
-      <c r="B90" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C90" s="9" t="s">
+      <c r="B90" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C90" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D90" s="9" t="s">
+      <c r="D90" s="7" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="91" spans="2:4" ht="34" customHeight="1">
-      <c r="B91" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C91" s="10" t="s">
+      <c r="B91" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C91" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="D91" s="10" t="s">
+      <c r="D91" s="8" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="92" spans="2:4" ht="34" customHeight="1">
-      <c r="B92" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C92" s="9" t="s">
+      <c r="B92" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C92" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="D92" s="9" t="s">
+      <c r="D92" s="7" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="93" spans="2:4" ht="34" customHeight="1">
-      <c r="B93" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C93" s="10" t="s">
+      <c r="B93" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C93" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="D93" s="10" t="s">
+      <c r="D93" s="8" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="94" spans="2:4" ht="34" customHeight="1">
-      <c r="B94" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C94" s="9" t="s">
+      <c r="B94" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C94" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="D94" s="9" t="s">
+      <c r="D94" s="7" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="95" spans="2:4" ht="34" customHeight="1">
-      <c r="B95" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C95" s="10" t="s">
+      <c r="B95" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C95" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="D95" s="10" t="s">
+      <c r="D95" s="8" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="96" spans="2:4" ht="34" customHeight="1">
-      <c r="B96" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C96" s="9" t="s">
+      <c r="B96" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C96" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="D96" s="9" t="s">
+      <c r="D96" s="7" t="s">
         <v>177</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B88:D88"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B88:D88"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFB923C"/>
   </sheetPr>
-  <dimension ref="B2:D45"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="B2:E45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" customWidth="1"/>
-    <col min="2" max="2" width="44.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" customWidth="1"/>
-    <col min="4" max="4" width="64.7109375" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" customWidth="1"/>
+    <col min="2" max="2" width="44.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
+    <col min="4" max="4" width="64.6640625" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" style="21"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="32" customHeight="1">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:5" ht="32" customHeight="1">
+      <c r="B2" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="2:4" ht="36" customHeight="1">
-      <c r="B3" s="2" t="s">
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+    </row>
+    <row r="3" spans="2:5" ht="36" customHeight="1">
+      <c r="B3" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="5" spans="2:4" ht="24" customHeight="1">
-      <c r="B5" s="3" t="s">
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+    </row>
+    <row r="5" spans="2:5" ht="24" customHeight="1">
+      <c r="B5" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="2:4" ht="22" customHeight="1">
-      <c r="B6" s="7" t="s">
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+    </row>
+    <row r="6" spans="2:5" ht="22" customHeight="1">
+      <c r="B6" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="5" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="24" customHeight="1">
-      <c r="B7" s="5" t="s">
+    <row r="7" spans="2:5" ht="24" customHeight="1">
+      <c r="B7" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="11">
-        <v>470</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="C7" s="9">
+        <v>400</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="8" spans="2:4" ht="24" customHeight="1">
-      <c r="B8" s="5" t="s">
+      <c r="E7" s="21" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="24" customHeight="1">
+      <c r="B8" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="9">
         <v>95</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="24" customHeight="1">
-      <c r="B9" s="5" t="s">
+    <row r="9" spans="2:5" ht="24" customHeight="1">
+      <c r="B9" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="9">
         <v>120</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="24" customHeight="1">
-      <c r="B10" s="5" t="s">
+    <row r="10" spans="2:5" ht="24" customHeight="1">
+      <c r="B10" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="9">
         <v>4</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="24" customHeight="1">
-      <c r="B11" s="5" t="s">
+    <row r="11" spans="2:5" ht="24" customHeight="1">
+      <c r="B11" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="9">
         <v>33</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="24" customHeight="1">
-      <c r="B12" s="5" t="s">
+    <row r="12" spans="2:5" ht="24" customHeight="1">
+      <c r="B12" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="9">
         <v>250</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="24" customHeight="1">
-      <c r="B13" s="5" t="s">
+    <row r="13" spans="2:5" ht="24" customHeight="1">
+      <c r="B13" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="10">
         <f>SUM(C7:C12)</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="24" customHeight="1">
-      <c r="B15" s="3" t="s">
+    <row r="15" spans="2:5" ht="24" customHeight="1">
+      <c r="B15" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="2:4" ht="22" customHeight="1">
-      <c r="B16" s="7" t="s">
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+    </row>
+    <row r="16" spans="2:5" ht="22" customHeight="1">
+      <c r="B16" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="5" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="22" customHeight="1">
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="9">
         <v>120</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="22" customHeight="1">
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="9">
         <v>350</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="22" customHeight="1">
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="9">
         <v>250</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="22" customHeight="1">
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="9">
         <v>1000</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="22" customHeight="1">
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="9">
         <v>95</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="22" spans="2:4" ht="22" customHeight="1">
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="9">
         <v>1000</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="3" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="24" spans="2:4" ht="24" customHeight="1">
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
     </row>
     <row r="25" spans="2:4" ht="22" customHeight="1">
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="5" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="28" customHeight="1">
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C26" s="9">
         <v>120</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="3" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="27" spans="2:4" ht="24" customHeight="1">
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="9">
         <v>10</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="3" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="28" spans="2:4" ht="28" customHeight="1">
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="C28" s="13">
+      <c r="C28" s="11">
         <v>4</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="3" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="30" spans="2:4" ht="24" customHeight="1">
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
     </row>
     <row r="31" spans="2:4" ht="22" customHeight="1">
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="5" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="32" spans="2:4" ht="24" customHeight="1">
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="C32" s="11">
+      <c r="C32" s="9">
         <v>1300</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="3" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="33" spans="2:4" ht="24" customHeight="1">
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="C33" s="11">
+      <c r="C33" s="9">
         <v>2500</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="3" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="34" spans="2:4" ht="24" customHeight="1">
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="C34" s="11">
+      <c r="C34" s="9">
         <v>4800</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="3" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="35" spans="2:4" ht="24" customHeight="1">
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="C35" s="13">
+      <c r="C35" s="11">
         <v>36</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="3" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="36" spans="2:4" ht="24" customHeight="1">
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="C36" s="11">
+      <c r="C36" s="9">
         <v>30</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="3" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="37" spans="2:4" ht="24" customHeight="1">
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="9">
         <v>18</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="3" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="38" spans="2:4" ht="24" customHeight="1">
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="9">
         <v>2</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="3" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="40" spans="2:4" ht="28" customHeight="1">
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="C40" s="12">
+      <c r="C40" s="10">
         <f>ROUND('Cost Inputs'!$C$33/'Cost Inputs'!$C$35+'Cost Inputs'!$C$36+'Cost Inputs'!$C$37+'Cost Inputs'!$C$38,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D40" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="42" spans="2:4" ht="24" customHeight="1">
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="16" t="s">
         <v>236</v>
       </c>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
     </row>
     <row r="43" spans="2:4" ht="22" customHeight="1">
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D43" s="5" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="44" spans="2:4" ht="24" customHeight="1">
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="C44" s="11">
+      <c r="C44" s="9">
         <v>1500</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="3" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="45" spans="2:4" ht="24" customHeight="1">
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="C45" s="11">
+      <c r="C45" s="9">
         <v>2500</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="3" t="s">
         <v>240</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B42:D42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFB923C"/>
   </sheetPr>
-  <dimension ref="B2:F23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="B2:F34"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" customWidth="1"/>
-    <col min="2" max="5" width="18.7109375" customWidth="1"/>
-    <col min="6" max="6" width="60.7109375" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" customWidth="1"/>
+    <col min="2" max="5" width="18.6640625" customWidth="1"/>
+    <col min="6" max="6" width="60.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="32" customHeight="1">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="18" t="s">
         <v>241</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
     </row>
     <row r="3" spans="2:6" ht="36" customHeight="1">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
     </row>
     <row r="5" spans="2:6" ht="24" customHeight="1">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
     </row>
     <row r="6" spans="2:6" ht="22" customHeight="1">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="5" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="24" customHeight="1">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="C7" s="11">
-        <v>80</v>
-      </c>
-      <c r="D7" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="E7" s="15">
+      <c r="C7" s="9"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="13">
         <f>C7*D7</f>
         <v>0</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="24" customHeight="1">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="9">
         <v>150</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="12">
         <v>0.5</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="13">
         <f>C8*D8</f>
+        <v>75</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="24" customHeight="1">
+      <c r="B9" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="C9" s="9">
+        <v>250</v>
+      </c>
+      <c r="D9" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="E9" s="13">
+        <f>C9*D9</f>
+        <v>50</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="24" customHeight="1">
+      <c r="B10" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C10" s="9">
+        <v>400</v>
+      </c>
+      <c r="D10" s="12">
         <v>0</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" ht="24" customHeight="1">
-      <c r="B9" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="C9" s="11">
-        <v>250</v>
-      </c>
-      <c r="D9" s="14">
-        <v>0.2</v>
-      </c>
-      <c r="E9" s="15">
-        <f>C9*D9</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" ht="24" customHeight="1">
-      <c r="B10" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="C10" s="11">
-        <v>400</v>
-      </c>
-      <c r="D10" s="14">
-        <v>0</v>
-      </c>
-      <c r="E10" s="15">
+      <c r="E10" s="13">
         <f>C10*D10</f>
         <v>0</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="22" customHeight="1">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="13">
         <f>SUM(D7:D10)</f>
+        <v>0.7</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="24" customHeight="1">
+      <c r="B12" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E12" s="10">
+        <f>SUMPRODUCT(C7:C10,D7:D10)/MAX(SUM(D7:D10),0.0001)</f>
+        <v>178.57142857142858</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="24" customHeight="1">
+      <c r="B14" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+    </row>
+    <row r="15" spans="2:6" ht="22" customHeight="1">
+      <c r="B15" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" ht="24" customHeight="1">
+      <c r="B16" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D16" s="12">
+        <v>0.15</v>
+      </c>
+      <c r="E16" s="9">
+        <v>25</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" ht="24" customHeight="1">
+      <c r="B17" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D17" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="E17" s="9">
         <v>0</v>
       </c>
-      <c r="F11" s="16" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" ht="24" customHeight="1">
-      <c r="B12" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="E12" s="12">
-        <f>SUMPRODUCT(C7:C10,D7:D10)/MAX(SUM(D7:D10),0.0001)</f>
+      <c r="F17" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" ht="24" customHeight="1">
+      <c r="B18" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D18" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="E18" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="2:6" ht="24" customHeight="1">
-      <c r="B14" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="2:6" ht="22" customHeight="1">
-      <c r="B15" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" ht="24" customHeight="1">
-      <c r="B16" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="D16" s="14">
-        <v>0.15</v>
-      </c>
-      <c r="E16" s="11">
-        <v>25</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" ht="24" customHeight="1">
-      <c r="B17" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="D17" s="14">
+      <c r="F18" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" ht="24" customHeight="1">
+      <c r="B19" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="D19" s="12">
         <v>0.4</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E19" s="9">
         <v>0</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" ht="24" customHeight="1">
-      <c r="B18" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="D18" s="14">
-        <v>0.05</v>
-      </c>
-      <c r="E18" s="11">
-        <v>0</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" ht="24" customHeight="1">
-      <c r="B19" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="D19" s="14">
-        <v>0.4</v>
-      </c>
-      <c r="E19" s="11">
-        <v>0</v>
-      </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="3" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="22" customHeight="1">
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="13">
         <f>SUM(D16:D19)</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="14" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="22" spans="2:6" ht="22" customHeight="1">
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="13">
         <f>'Tier Pricing'!$D$16+'Tier Pricing'!$D$17+'Tier Pricing'!$D$18</f>
-        <v>0</v>
-      </c>
-      <c r="F22" s="16" t="s">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="F22" s="14" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="23" spans="2:6" ht="28" customHeight="1">
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="10">
         <f>'Tier Pricing'!$E$12+'Tier Pricing'!$D$22*'Cost Inputs'!$C$40+'Tier Pricing'!$D$16*'Tier Pricing'!$E$16</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="16" t="s">
+        <v>253.72142857142859</v>
+      </c>
+      <c r="F23" s="14" t="s">
         <v>280</v>
       </c>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="C28" t="s">
+        <v>250</v>
+      </c>
+      <c r="E28" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="C32" s="22" t="s">
+        <v>324</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3">
+      <c r="C33" s="22" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3">
+      <c r="C34" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3399,1707 +3514,1707 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor rgb="FF0D9488"/>
   </sheetPr>
   <dimension ref="B2:L43"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="12" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" customWidth="1"/>
+    <col min="3" max="12" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="32" customHeight="1">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="18" t="s">
         <v>281</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
     </row>
     <row r="3" spans="2:12" ht="36" customHeight="1">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="19" t="s">
         <v>282</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
     </row>
     <row r="6" spans="2:12" ht="30" customHeight="1">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="5" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="20" customHeight="1">
-      <c r="B7" s="15">
+      <c r="B7" s="13">
         <v>1</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="11">
         <v>1</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="13">
         <f>C7</f>
+        <v>1</v>
+      </c>
+      <c r="E7" s="13">
+        <f>C7*'Cost Inputs'!$C$44</f>
+        <v>1500</v>
+      </c>
+      <c r="F7" s="13">
+        <f>D7*'Tier Pricing'!$E$23</f>
+        <v>253.72142857142859</v>
+      </c>
+      <c r="G7" s="10">
+        <f t="shared" ref="G7:G42" si="0">E7+F7</f>
+        <v>1753.7214285714285</v>
+      </c>
+      <c r="H7" s="13">
+        <f>'Cost Inputs'!$C$13+IF(D7&gt;=10,'Cost Inputs'!$C$17,0)+IF(D7&gt;=20,'Cost Inputs'!$C$18,0)+IF(D7&gt;=30,'Cost Inputs'!$C$19,0)+IF(D7&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
+        <v>902</v>
+      </c>
+      <c r="I7" s="13">
+        <f>IF(D7&lt;='Cost Inputs'!$C$28,D7*'Cost Inputs'!$C$26,D7*'Cost Inputs'!$C$27)+D7*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
+        <v>191.4</v>
+      </c>
+      <c r="J7" s="13">
+        <f t="shared" ref="J7:J42" si="1">H7+I7</f>
+        <v>1093.4000000000001</v>
+      </c>
+      <c r="K7" s="15">
+        <f t="shared" ref="K7:K42" si="2">G7-J7</f>
+        <v>660.32142857142844</v>
+      </c>
+      <c r="L7" s="15">
+        <f>K7</f>
+        <v>660.32142857142844</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="20" customHeight="1">
+      <c r="B8" s="13">
+        <v>2</v>
+      </c>
+      <c r="C8" s="11">
         <v>0</v>
       </c>
-      <c r="E7" s="15">
-        <f>C7*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="15">
-        <f>D7*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="12">
-        <f>E7+F7</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="15">
-        <f>'Cost Inputs'!$C$13+IF(D7&gt;=10,'Cost Inputs'!$C$17,0)+IF(D7&gt;=20,'Cost Inputs'!$C$18,0)+IF(D7&gt;=30,'Cost Inputs'!$C$19,0)+IF(D7&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="15">
-        <f>IF(D7&lt;='Cost Inputs'!$C$28,D7*'Cost Inputs'!$C$26,D7*'Cost Inputs'!$C$27)+D7*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="15">
-        <f>H7+I7</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="17">
-        <f>G7-J7</f>
-        <v>0</v>
-      </c>
-      <c r="L7" s="17">
-        <f>K7</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="20" customHeight="1">
-      <c r="B8" s="15">
-        <v>2</v>
-      </c>
-      <c r="C8" s="13">
-        <v>0</v>
-      </c>
-      <c r="D8" s="15">
-        <f>D7+C8</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="15">
+      <c r="D8" s="13">
+        <f t="shared" ref="D8:D42" si="3">D7+C8</f>
+        <v>1</v>
+      </c>
+      <c r="E8" s="13">
         <f>C8*'Cost Inputs'!$C$44</f>
         <v>0</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="13">
         <f>D8*'Tier Pricing'!$E$23</f>
+        <v>253.72142857142859</v>
+      </c>
+      <c r="G8" s="10">
+        <f t="shared" si="0"/>
+        <v>253.72142857142859</v>
+      </c>
+      <c r="H8" s="13">
+        <f>'Cost Inputs'!$C$13+IF(D8&gt;=10,'Cost Inputs'!$C$17,0)+IF(D8&gt;=20,'Cost Inputs'!$C$18,0)+IF(D8&gt;=30,'Cost Inputs'!$C$19,0)+IF(D8&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
+        <v>902</v>
+      </c>
+      <c r="I8" s="13">
+        <f>IF(D8&lt;='Cost Inputs'!$C$28,D8*'Cost Inputs'!$C$26,D8*'Cost Inputs'!$C$27)+D8*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
+        <v>191.4</v>
+      </c>
+      <c r="J8" s="13">
+        <f t="shared" si="1"/>
+        <v>1093.4000000000001</v>
+      </c>
+      <c r="K8" s="15">
+        <f t="shared" si="2"/>
+        <v>-839.67857142857156</v>
+      </c>
+      <c r="L8" s="15">
+        <f t="shared" ref="L8:L42" si="4">L7+K8</f>
+        <v>-179.35714285714312</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="20" customHeight="1">
+      <c r="B9" s="13">
+        <v>3</v>
+      </c>
+      <c r="C9" s="11">
         <v>0</v>
       </c>
-      <c r="G8" s="12">
-        <f>E8+F8</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="15">
-        <f>'Cost Inputs'!$C$13+IF(D8&gt;=10,'Cost Inputs'!$C$17,0)+IF(D8&gt;=20,'Cost Inputs'!$C$18,0)+IF(D8&gt;=30,'Cost Inputs'!$C$19,0)+IF(D8&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="15">
-        <f>IF(D8&lt;='Cost Inputs'!$C$28,D8*'Cost Inputs'!$C$26,D8*'Cost Inputs'!$C$27)+D8*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J8" s="15">
-        <f>H8+I8</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="17">
-        <f>G8-J8</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="17">
-        <f>L7+K8</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="20" customHeight="1">
-      <c r="B9" s="15">
-        <v>3</v>
-      </c>
-      <c r="C9" s="13">
-        <v>0</v>
-      </c>
-      <c r="D9" s="15">
-        <f>D8+C9</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="15">
+      <c r="D9" s="13">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="E9" s="13">
         <f>C9*'Cost Inputs'!$C$44</f>
         <v>0</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="13">
         <f>D9*'Tier Pricing'!$E$23</f>
+        <v>253.72142857142859</v>
+      </c>
+      <c r="G9" s="10">
+        <f t="shared" si="0"/>
+        <v>253.72142857142859</v>
+      </c>
+      <c r="H9" s="13">
+        <f>'Cost Inputs'!$C$13+IF(D9&gt;=10,'Cost Inputs'!$C$17,0)+IF(D9&gt;=20,'Cost Inputs'!$C$18,0)+IF(D9&gt;=30,'Cost Inputs'!$C$19,0)+IF(D9&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
+        <v>902</v>
+      </c>
+      <c r="I9" s="13">
+        <f>IF(D9&lt;='Cost Inputs'!$C$28,D9*'Cost Inputs'!$C$26,D9*'Cost Inputs'!$C$27)+D9*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
+        <v>191.4</v>
+      </c>
+      <c r="J9" s="13">
+        <f t="shared" si="1"/>
+        <v>1093.4000000000001</v>
+      </c>
+      <c r="K9" s="15">
+        <f t="shared" si="2"/>
+        <v>-839.67857142857156</v>
+      </c>
+      <c r="L9" s="15">
+        <f t="shared" si="4"/>
+        <v>-1019.0357142857147</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="20" customHeight="1">
+      <c r="B10" s="13">
+        <v>4</v>
+      </c>
+      <c r="C10" s="11">
+        <v>1</v>
+      </c>
+      <c r="D10" s="13">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="E10" s="13">
+        <f>C10*'Cost Inputs'!$C$44</f>
+        <v>1500</v>
+      </c>
+      <c r="F10" s="13">
+        <f>D10*'Tier Pricing'!$E$23</f>
+        <v>507.44285714285718</v>
+      </c>
+      <c r="G10" s="10">
+        <f t="shared" si="0"/>
+        <v>2007.4428571428571</v>
+      </c>
+      <c r="H10" s="13">
+        <f>'Cost Inputs'!$C$13+IF(D10&gt;=10,'Cost Inputs'!$C$17,0)+IF(D10&gt;=20,'Cost Inputs'!$C$18,0)+IF(D10&gt;=30,'Cost Inputs'!$C$19,0)+IF(D10&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
+        <v>902</v>
+      </c>
+      <c r="I10" s="13">
+        <f>IF(D10&lt;='Cost Inputs'!$C$28,D10*'Cost Inputs'!$C$26,D10*'Cost Inputs'!$C$27)+D10*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
+        <v>382.8</v>
+      </c>
+      <c r="J10" s="13">
+        <f t="shared" si="1"/>
+        <v>1284.8</v>
+      </c>
+      <c r="K10" s="15">
+        <f t="shared" si="2"/>
+        <v>722.64285714285711</v>
+      </c>
+      <c r="L10" s="15">
+        <f t="shared" si="4"/>
+        <v>-296.39285714285757</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="20" customHeight="1">
+      <c r="B11" s="13">
+        <v>5</v>
+      </c>
+      <c r="C11" s="11">
+        <v>1</v>
+      </c>
+      <c r="D11" s="13">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="E11" s="13">
+        <f>C11*'Cost Inputs'!$C$44</f>
+        <v>1500</v>
+      </c>
+      <c r="F11" s="13">
+        <f>D11*'Tier Pricing'!$E$23</f>
+        <v>761.16428571428582</v>
+      </c>
+      <c r="G11" s="10">
+        <f t="shared" si="0"/>
+        <v>2261.1642857142861</v>
+      </c>
+      <c r="H11" s="13">
+        <f>'Cost Inputs'!$C$13+IF(D11&gt;=10,'Cost Inputs'!$C$17,0)+IF(D11&gt;=20,'Cost Inputs'!$C$18,0)+IF(D11&gt;=30,'Cost Inputs'!$C$19,0)+IF(D11&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
+        <v>902</v>
+      </c>
+      <c r="I11" s="13">
+        <f>IF(D11&lt;='Cost Inputs'!$C$28,D11*'Cost Inputs'!$C$26,D11*'Cost Inputs'!$C$27)+D11*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
+        <v>574.20000000000005</v>
+      </c>
+      <c r="J11" s="13">
+        <f t="shared" si="1"/>
+        <v>1476.2</v>
+      </c>
+      <c r="K11" s="15">
+        <f t="shared" si="2"/>
+        <v>784.96428571428601</v>
+      </c>
+      <c r="L11" s="15">
+        <f t="shared" si="4"/>
+        <v>488.57142857142844</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="20" customHeight="1">
+      <c r="B12" s="13">
+        <v>6</v>
+      </c>
+      <c r="C12" s="11">
         <v>0</v>
       </c>
-      <c r="G9" s="12">
-        <f>E9+F9</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="15">
-        <f>'Cost Inputs'!$C$13+IF(D9&gt;=10,'Cost Inputs'!$C$17,0)+IF(D9&gt;=20,'Cost Inputs'!$C$18,0)+IF(D9&gt;=30,'Cost Inputs'!$C$19,0)+IF(D9&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="15">
-        <f>IF(D9&lt;='Cost Inputs'!$C$28,D9*'Cost Inputs'!$C$26,D9*'Cost Inputs'!$C$27)+D9*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="15">
-        <f>H9+I9</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="17">
-        <f>G9-J9</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="17">
-        <f>L8+K9</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="20" customHeight="1">
-      <c r="B10" s="15">
-        <v>4</v>
-      </c>
-      <c r="C10" s="13">
-        <v>1</v>
-      </c>
-      <c r="D10" s="15">
-        <f>D9+C10</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="15">
-        <f>C10*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="15">
-        <f>D10*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="12">
-        <f>E10+F10</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="15">
-        <f>'Cost Inputs'!$C$13+IF(D10&gt;=10,'Cost Inputs'!$C$17,0)+IF(D10&gt;=20,'Cost Inputs'!$C$18,0)+IF(D10&gt;=30,'Cost Inputs'!$C$19,0)+IF(D10&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="15">
-        <f>IF(D10&lt;='Cost Inputs'!$C$28,D10*'Cost Inputs'!$C$26,D10*'Cost Inputs'!$C$27)+D10*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="15">
-        <f>H10+I10</f>
-        <v>0</v>
-      </c>
-      <c r="K10" s="17">
-        <f>G10-J10</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="17">
-        <f>L9+K10</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="20" customHeight="1">
-      <c r="B11" s="15">
-        <v>5</v>
-      </c>
-      <c r="C11" s="13">
-        <v>1</v>
-      </c>
-      <c r="D11" s="15">
-        <f>D10+C11</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="15">
-        <f>C11*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="15">
-        <f>D11*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="12">
-        <f>E11+F11</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="15">
-        <f>'Cost Inputs'!$C$13+IF(D11&gt;=10,'Cost Inputs'!$C$17,0)+IF(D11&gt;=20,'Cost Inputs'!$C$18,0)+IF(D11&gt;=30,'Cost Inputs'!$C$19,0)+IF(D11&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="15">
-        <f>IF(D11&lt;='Cost Inputs'!$C$28,D11*'Cost Inputs'!$C$26,D11*'Cost Inputs'!$C$27)+D11*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="15">
-        <f>H11+I11</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="17">
-        <f>G11-J11</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="17">
-        <f>L10+K11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="20" customHeight="1">
-      <c r="B12" s="15">
-        <v>6</v>
-      </c>
-      <c r="C12" s="13">
-        <v>0</v>
-      </c>
-      <c r="D12" s="15">
-        <f>D11+C12</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="15">
+      <c r="D12" s="13">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="E12" s="13">
         <f>C12*'Cost Inputs'!$C$44</f>
         <v>0</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="13">
         <f>D12*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="12">
-        <f>E12+F12</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="15">
+        <v>761.16428571428582</v>
+      </c>
+      <c r="G12" s="10">
+        <f t="shared" si="0"/>
+        <v>761.16428571428582</v>
+      </c>
+      <c r="H12" s="13">
         <f>'Cost Inputs'!$C$13+IF(D12&gt;=10,'Cost Inputs'!$C$17,0)+IF(D12&gt;=20,'Cost Inputs'!$C$18,0)+IF(D12&gt;=30,'Cost Inputs'!$C$19,0)+IF(D12&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="15">
+        <v>902</v>
+      </c>
+      <c r="I12" s="13">
         <f>IF(D12&lt;='Cost Inputs'!$C$28,D12*'Cost Inputs'!$C$26,D12*'Cost Inputs'!$C$27)+D12*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="15">
-        <f>H12+I12</f>
-        <v>0</v>
-      </c>
-      <c r="K12" s="17">
-        <f>G12-J12</f>
-        <v>0</v>
-      </c>
-      <c r="L12" s="17">
-        <f>L11+K12</f>
-        <v>0</v>
+        <v>574.20000000000005</v>
+      </c>
+      <c r="J12" s="13">
+        <f t="shared" si="1"/>
+        <v>1476.2</v>
+      </c>
+      <c r="K12" s="15">
+        <f t="shared" si="2"/>
+        <v>-715.03571428571422</v>
+      </c>
+      <c r="L12" s="15">
+        <f t="shared" si="4"/>
+        <v>-226.46428571428578</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="20" customHeight="1">
-      <c r="B13" s="15">
+      <c r="B13" s="13">
         <v>7</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="11">
         <v>1</v>
       </c>
-      <c r="D13" s="15">
-        <f>D12+C13</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="15">
+      <c r="D13" s="13">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="E13" s="13">
         <f>C13*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="15">
+        <v>1500</v>
+      </c>
+      <c r="F13" s="13">
         <f>D13*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="12">
-        <f>E13+F13</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="15">
+        <v>1014.8857142857144</v>
+      </c>
+      <c r="G13" s="10">
+        <f t="shared" si="0"/>
+        <v>2514.8857142857141</v>
+      </c>
+      <c r="H13" s="13">
         <f>'Cost Inputs'!$C$13+IF(D13&gt;=10,'Cost Inputs'!$C$17,0)+IF(D13&gt;=20,'Cost Inputs'!$C$18,0)+IF(D13&gt;=30,'Cost Inputs'!$C$19,0)+IF(D13&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="15">
+        <v>902</v>
+      </c>
+      <c r="I13" s="13">
         <f>IF(D13&lt;='Cost Inputs'!$C$28,D13*'Cost Inputs'!$C$26,D13*'Cost Inputs'!$C$27)+D13*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="15">
-        <f>H13+I13</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="17">
-        <f>G13-J13</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="17">
-        <f>L12+K13</f>
-        <v>0</v>
+        <v>765.6</v>
+      </c>
+      <c r="J13" s="13">
+        <f t="shared" si="1"/>
+        <v>1667.6</v>
+      </c>
+      <c r="K13" s="15">
+        <f t="shared" si="2"/>
+        <v>847.28571428571422</v>
+      </c>
+      <c r="L13" s="15">
+        <f t="shared" si="4"/>
+        <v>620.82142857142844</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="20" customHeight="1">
-      <c r="B14" s="15">
+      <c r="B14" s="13">
         <v>8</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="11">
         <v>1</v>
       </c>
-      <c r="D14" s="15">
-        <f>D13+C14</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="15">
+      <c r="D14" s="13">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="E14" s="13">
         <f>C14*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="15">
+        <v>1500</v>
+      </c>
+      <c r="F14" s="13">
         <f>D14*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="12">
-        <f>E14+F14</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="15">
+        <v>1268.6071428571429</v>
+      </c>
+      <c r="G14" s="10">
+        <f t="shared" si="0"/>
+        <v>2768.6071428571431</v>
+      </c>
+      <c r="H14" s="13">
         <f>'Cost Inputs'!$C$13+IF(D14&gt;=10,'Cost Inputs'!$C$17,0)+IF(D14&gt;=20,'Cost Inputs'!$C$18,0)+IF(D14&gt;=30,'Cost Inputs'!$C$19,0)+IF(D14&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="15">
+        <v>902</v>
+      </c>
+      <c r="I14" s="13">
         <f>IF(D14&lt;='Cost Inputs'!$C$28,D14*'Cost Inputs'!$C$26,D14*'Cost Inputs'!$C$27)+D14*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="15">
-        <f>H14+I14</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="17">
-        <f>G14-J14</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="17">
-        <f>L13+K14</f>
-        <v>0</v>
+        <v>407.00000000000006</v>
+      </c>
+      <c r="J14" s="13">
+        <f t="shared" si="1"/>
+        <v>1309</v>
+      </c>
+      <c r="K14" s="15">
+        <f t="shared" si="2"/>
+        <v>1459.6071428571431</v>
+      </c>
+      <c r="L14" s="15">
+        <f t="shared" si="4"/>
+        <v>2080.4285714285716</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="20" customHeight="1">
-      <c r="B15" s="15">
+      <c r="B15" s="13">
         <v>9</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="11">
         <v>1</v>
       </c>
-      <c r="D15" s="15">
-        <f>D14+C15</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="15">
+      <c r="D15" s="13">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="E15" s="13">
         <f>C15*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="15">
+        <v>1500</v>
+      </c>
+      <c r="F15" s="13">
         <f>D15*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="12">
-        <f>E15+F15</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="15">
+        <v>1522.3285714285716</v>
+      </c>
+      <c r="G15" s="10">
+        <f t="shared" si="0"/>
+        <v>3022.3285714285716</v>
+      </c>
+      <c r="H15" s="13">
         <f>'Cost Inputs'!$C$13+IF(D15&gt;=10,'Cost Inputs'!$C$17,0)+IF(D15&gt;=20,'Cost Inputs'!$C$18,0)+IF(D15&gt;=30,'Cost Inputs'!$C$19,0)+IF(D15&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="15">
+        <v>902</v>
+      </c>
+      <c r="I15" s="13">
         <f>IF(D15&lt;='Cost Inputs'!$C$28,D15*'Cost Inputs'!$C$26,D15*'Cost Inputs'!$C$27)+D15*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="15">
-        <f>H15+I15</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="17">
-        <f>G15-J15</f>
-        <v>0</v>
-      </c>
-      <c r="L15" s="17">
-        <f>L14+K15</f>
-        <v>0</v>
+        <v>488.40000000000009</v>
+      </c>
+      <c r="J15" s="13">
+        <f t="shared" si="1"/>
+        <v>1390.4</v>
+      </c>
+      <c r="K15" s="15">
+        <f t="shared" si="2"/>
+        <v>1631.9285714285716</v>
+      </c>
+      <c r="L15" s="15">
+        <f t="shared" si="4"/>
+        <v>3712.3571428571431</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="20" customHeight="1">
-      <c r="B16" s="15">
+      <c r="B16" s="13">
         <v>10</v>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="11">
         <v>2</v>
       </c>
-      <c r="D16" s="15">
-        <f>D15+C16</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="15">
+      <c r="D16" s="13">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="E16" s="13">
         <f>C16*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="15">
+        <v>3000</v>
+      </c>
+      <c r="F16" s="13">
         <f>D16*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="12">
-        <f>E16+F16</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="15">
+        <v>2029.7714285714287</v>
+      </c>
+      <c r="G16" s="10">
+        <f t="shared" si="0"/>
+        <v>5029.7714285714283</v>
+      </c>
+      <c r="H16" s="13">
         <f>'Cost Inputs'!$C$13+IF(D16&gt;=10,'Cost Inputs'!$C$17,0)+IF(D16&gt;=20,'Cost Inputs'!$C$18,0)+IF(D16&gt;=30,'Cost Inputs'!$C$19,0)+IF(D16&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="15">
+        <v>902</v>
+      </c>
+      <c r="I16" s="13">
         <f>IF(D16&lt;='Cost Inputs'!$C$28,D16*'Cost Inputs'!$C$26,D16*'Cost Inputs'!$C$27)+D16*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="15">
-        <f>H16+I16</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="17">
-        <f>G16-J16</f>
-        <v>0</v>
-      </c>
-      <c r="L16" s="17">
-        <f>L15+K16</f>
-        <v>0</v>
+        <v>651.20000000000005</v>
+      </c>
+      <c r="J16" s="13">
+        <f t="shared" si="1"/>
+        <v>1553.2</v>
+      </c>
+      <c r="K16" s="15">
+        <f t="shared" si="2"/>
+        <v>3476.5714285714284</v>
+      </c>
+      <c r="L16" s="15">
+        <f t="shared" si="4"/>
+        <v>7188.9285714285716</v>
       </c>
     </row>
     <row r="17" spans="2:12" ht="20" customHeight="1">
-      <c r="B17" s="15">
+      <c r="B17" s="13">
         <v>11</v>
       </c>
-      <c r="C17" s="13">
+      <c r="C17" s="11">
         <v>2</v>
       </c>
-      <c r="D17" s="15">
-        <f>D16+C17</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="15">
+      <c r="D17" s="13">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="E17" s="13">
         <f>C17*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="15">
+        <v>3000</v>
+      </c>
+      <c r="F17" s="13">
         <f>D17*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="12">
-        <f>E17+F17</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="15">
+        <v>2537.2142857142858</v>
+      </c>
+      <c r="G17" s="10">
+        <f t="shared" si="0"/>
+        <v>5537.2142857142862</v>
+      </c>
+      <c r="H17" s="13">
         <f>'Cost Inputs'!$C$13+IF(D17&gt;=10,'Cost Inputs'!$C$17,0)+IF(D17&gt;=20,'Cost Inputs'!$C$18,0)+IF(D17&gt;=30,'Cost Inputs'!$C$19,0)+IF(D17&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="15">
+        <v>1022</v>
+      </c>
+      <c r="I17" s="13">
         <f>IF(D17&lt;='Cost Inputs'!$C$28,D17*'Cost Inputs'!$C$26,D17*'Cost Inputs'!$C$27)+D17*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="15">
-        <f>H17+I17</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="17">
-        <f>G17-J17</f>
-        <v>0</v>
-      </c>
-      <c r="L17" s="17">
-        <f>L16+K17</f>
-        <v>0</v>
+        <v>814.00000000000011</v>
+      </c>
+      <c r="J17" s="13">
+        <f t="shared" si="1"/>
+        <v>1836</v>
+      </c>
+      <c r="K17" s="15">
+        <f t="shared" si="2"/>
+        <v>3701.2142857142862</v>
+      </c>
+      <c r="L17" s="15">
+        <f t="shared" si="4"/>
+        <v>10890.142857142859</v>
       </c>
     </row>
     <row r="18" spans="2:12" ht="20" customHeight="1">
-      <c r="B18" s="15">
+      <c r="B18" s="13">
         <v>12</v>
       </c>
-      <c r="C18" s="13">
+      <c r="C18" s="11">
         <v>2</v>
       </c>
-      <c r="D18" s="15">
-        <f>D17+C18</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="15">
+      <c r="D18" s="13">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="E18" s="13">
         <f>C18*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="15">
+        <v>3000</v>
+      </c>
+      <c r="F18" s="13">
         <f>D18*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G18" s="12">
-        <f>E18+F18</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="15">
+        <v>3044.6571428571433</v>
+      </c>
+      <c r="G18" s="10">
+        <f t="shared" si="0"/>
+        <v>6044.6571428571433</v>
+      </c>
+      <c r="H18" s="13">
         <f>'Cost Inputs'!$C$13+IF(D18&gt;=10,'Cost Inputs'!$C$17,0)+IF(D18&gt;=20,'Cost Inputs'!$C$18,0)+IF(D18&gt;=30,'Cost Inputs'!$C$19,0)+IF(D18&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="15">
+        <v>1022</v>
+      </c>
+      <c r="I18" s="13">
         <f>IF(D18&lt;='Cost Inputs'!$C$28,D18*'Cost Inputs'!$C$26,D18*'Cost Inputs'!$C$27)+D18*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="15">
-        <f>H18+I18</f>
-        <v>0</v>
-      </c>
-      <c r="K18" s="17">
-        <f>G18-J18</f>
-        <v>0</v>
-      </c>
-      <c r="L18" s="17">
-        <f>L17+K18</f>
-        <v>0</v>
+        <v>976.80000000000018</v>
+      </c>
+      <c r="J18" s="13">
+        <f t="shared" si="1"/>
+        <v>1998.8000000000002</v>
+      </c>
+      <c r="K18" s="15">
+        <f t="shared" si="2"/>
+        <v>4045.8571428571431</v>
+      </c>
+      <c r="L18" s="15">
+        <f t="shared" si="4"/>
+        <v>14936.000000000002</v>
       </c>
     </row>
     <row r="19" spans="2:12" ht="20" customHeight="1">
-      <c r="B19" s="15">
+      <c r="B19" s="13">
         <v>13</v>
       </c>
-      <c r="C19" s="13">
+      <c r="C19" s="11">
         <v>2</v>
       </c>
-      <c r="D19" s="15">
-        <f>D18+C19</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="15">
+      <c r="D19" s="13">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="E19" s="13">
         <f>C19*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="15">
+        <v>3000</v>
+      </c>
+      <c r="F19" s="13">
         <f>D19*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G19" s="12">
-        <f>E19+F19</f>
-        <v>0</v>
-      </c>
-      <c r="H19" s="15">
+        <v>3552.1000000000004</v>
+      </c>
+      <c r="G19" s="10">
+        <f t="shared" si="0"/>
+        <v>6552.1</v>
+      </c>
+      <c r="H19" s="13">
         <f>'Cost Inputs'!$C$13+IF(D19&gt;=10,'Cost Inputs'!$C$17,0)+IF(D19&gt;=20,'Cost Inputs'!$C$18,0)+IF(D19&gt;=30,'Cost Inputs'!$C$19,0)+IF(D19&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I19" s="15">
+        <v>1022</v>
+      </c>
+      <c r="I19" s="13">
         <f>IF(D19&lt;='Cost Inputs'!$C$28,D19*'Cost Inputs'!$C$26,D19*'Cost Inputs'!$C$27)+D19*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="15">
-        <f>H19+I19</f>
-        <v>0</v>
-      </c>
-      <c r="K19" s="17">
-        <f>G19-J19</f>
-        <v>0</v>
-      </c>
-      <c r="L19" s="17">
-        <f>L18+K19</f>
-        <v>0</v>
+        <v>1139.6000000000004</v>
+      </c>
+      <c r="J19" s="13">
+        <f t="shared" si="1"/>
+        <v>2161.6000000000004</v>
+      </c>
+      <c r="K19" s="15">
+        <f t="shared" si="2"/>
+        <v>4390.5</v>
+      </c>
+      <c r="L19" s="15">
+        <f t="shared" si="4"/>
+        <v>19326.5</v>
       </c>
     </row>
     <row r="20" spans="2:12" ht="20" customHeight="1">
-      <c r="B20" s="15">
+      <c r="B20" s="13">
         <v>14</v>
       </c>
-      <c r="C20" s="13">
+      <c r="C20" s="11">
         <v>2</v>
       </c>
-      <c r="D20" s="15">
-        <f>D19+C20</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="15">
+      <c r="D20" s="13">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="E20" s="13">
         <f>C20*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="15">
+        <v>3000</v>
+      </c>
+      <c r="F20" s="13">
         <f>D20*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G20" s="12">
-        <f>E20+F20</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="15">
+        <v>4059.5428571428574</v>
+      </c>
+      <c r="G20" s="10">
+        <f t="shared" si="0"/>
+        <v>7059.5428571428574</v>
+      </c>
+      <c r="H20" s="13">
         <f>'Cost Inputs'!$C$13+IF(D20&gt;=10,'Cost Inputs'!$C$17,0)+IF(D20&gt;=20,'Cost Inputs'!$C$18,0)+IF(D20&gt;=30,'Cost Inputs'!$C$19,0)+IF(D20&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I20" s="15">
+        <v>1022</v>
+      </c>
+      <c r="I20" s="13">
         <f>IF(D20&lt;='Cost Inputs'!$C$28,D20*'Cost Inputs'!$C$26,D20*'Cost Inputs'!$C$27)+D20*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="15">
-        <f>H20+I20</f>
-        <v>0</v>
-      </c>
-      <c r="K20" s="17">
-        <f>G20-J20</f>
-        <v>0</v>
-      </c>
-      <c r="L20" s="17">
-        <f>L19+K20</f>
-        <v>0</v>
+        <v>1302.4000000000001</v>
+      </c>
+      <c r="J20" s="13">
+        <f t="shared" si="1"/>
+        <v>2324.4</v>
+      </c>
+      <c r="K20" s="15">
+        <f t="shared" si="2"/>
+        <v>4735.1428571428569</v>
+      </c>
+      <c r="L20" s="15">
+        <f t="shared" si="4"/>
+        <v>24061.642857142855</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="20" customHeight="1">
-      <c r="B21" s="15">
+      <c r="B21" s="13">
         <v>15</v>
       </c>
-      <c r="C21" s="13">
+      <c r="C21" s="11">
         <v>3</v>
       </c>
-      <c r="D21" s="15">
-        <f>D20+C21</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="15">
+      <c r="D21" s="13">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="E21" s="13">
         <f>C21*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F21" s="13">
         <f>D21*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G21" s="12">
-        <f>E21+F21</f>
-        <v>0</v>
-      </c>
-      <c r="H21" s="15">
+        <v>4820.7071428571435</v>
+      </c>
+      <c r="G21" s="10">
+        <f t="shared" si="0"/>
+        <v>9320.7071428571435</v>
+      </c>
+      <c r="H21" s="13">
         <f>'Cost Inputs'!$C$13+IF(D21&gt;=10,'Cost Inputs'!$C$17,0)+IF(D21&gt;=20,'Cost Inputs'!$C$18,0)+IF(D21&gt;=30,'Cost Inputs'!$C$19,0)+IF(D21&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I21" s="15">
+        <v>1022</v>
+      </c>
+      <c r="I21" s="13">
         <f>IF(D21&lt;='Cost Inputs'!$C$28,D21*'Cost Inputs'!$C$26,D21*'Cost Inputs'!$C$27)+D21*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="15">
-        <f>H21+I21</f>
-        <v>0</v>
-      </c>
-      <c r="K21" s="17">
-        <f>G21-J21</f>
-        <v>0</v>
-      </c>
-      <c r="L21" s="17">
-        <f>L20+K21</f>
-        <v>0</v>
+        <v>1546.6000000000004</v>
+      </c>
+      <c r="J21" s="13">
+        <f t="shared" si="1"/>
+        <v>2568.6000000000004</v>
+      </c>
+      <c r="K21" s="15">
+        <f t="shared" si="2"/>
+        <v>6752.1071428571431</v>
+      </c>
+      <c r="L21" s="15">
+        <f t="shared" si="4"/>
+        <v>30813.75</v>
       </c>
     </row>
     <row r="22" spans="2:12" ht="20" customHeight="1">
-      <c r="B22" s="15">
+      <c r="B22" s="13">
         <v>16</v>
       </c>
-      <c r="C22" s="13">
+      <c r="C22" s="11">
         <v>3</v>
       </c>
-      <c r="D22" s="15">
-        <f>D21+C22</f>
-        <v>0</v>
-      </c>
-      <c r="E22" s="15">
+      <c r="D22" s="13">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="E22" s="13">
         <f>C22*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F22" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F22" s="13">
         <f>D22*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G22" s="12">
-        <f>E22+F22</f>
-        <v>0</v>
-      </c>
-      <c r="H22" s="15">
+        <v>5581.8714285714286</v>
+      </c>
+      <c r="G22" s="10">
+        <f t="shared" si="0"/>
+        <v>10081.871428571429</v>
+      </c>
+      <c r="H22" s="13">
         <f>'Cost Inputs'!$C$13+IF(D22&gt;=10,'Cost Inputs'!$C$17,0)+IF(D22&gt;=20,'Cost Inputs'!$C$18,0)+IF(D22&gt;=30,'Cost Inputs'!$C$19,0)+IF(D22&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I22" s="15">
+        <v>2372</v>
+      </c>
+      <c r="I22" s="13">
         <f>IF(D22&lt;='Cost Inputs'!$C$28,D22*'Cost Inputs'!$C$26,D22*'Cost Inputs'!$C$27)+D22*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="15">
-        <f>H22+I22</f>
-        <v>0</v>
-      </c>
-      <c r="K22" s="17">
-        <f>G22-J22</f>
-        <v>0</v>
-      </c>
-      <c r="L22" s="17">
-        <f>L21+K22</f>
-        <v>0</v>
+        <v>1790.8000000000004</v>
+      </c>
+      <c r="J22" s="13">
+        <f t="shared" si="1"/>
+        <v>4162.8</v>
+      </c>
+      <c r="K22" s="15">
+        <f t="shared" si="2"/>
+        <v>5919.0714285714284</v>
+      </c>
+      <c r="L22" s="15">
+        <f t="shared" si="4"/>
+        <v>36732.821428571428</v>
       </c>
     </row>
     <row r="23" spans="2:12" ht="20" customHeight="1">
-      <c r="B23" s="15">
+      <c r="B23" s="13">
         <v>17</v>
       </c>
-      <c r="C23" s="13">
+      <c r="C23" s="11">
         <v>3</v>
       </c>
-      <c r="D23" s="15">
-        <f>D22+C23</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="15">
+      <c r="D23" s="13">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="E23" s="13">
         <f>C23*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F23" s="13">
         <f>D23*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G23" s="12">
-        <f>E23+F23</f>
-        <v>0</v>
-      </c>
-      <c r="H23" s="15">
+        <v>6343.0357142857147</v>
+      </c>
+      <c r="G23" s="10">
+        <f t="shared" si="0"/>
+        <v>10843.035714285714</v>
+      </c>
+      <c r="H23" s="13">
         <f>'Cost Inputs'!$C$13+IF(D23&gt;=10,'Cost Inputs'!$C$17,0)+IF(D23&gt;=20,'Cost Inputs'!$C$18,0)+IF(D23&gt;=30,'Cost Inputs'!$C$19,0)+IF(D23&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I23" s="15">
+        <v>2372</v>
+      </c>
+      <c r="I23" s="13">
         <f>IF(D23&lt;='Cost Inputs'!$C$28,D23*'Cost Inputs'!$C$26,D23*'Cost Inputs'!$C$27)+D23*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="15">
-        <f>H23+I23</f>
-        <v>0</v>
-      </c>
-      <c r="K23" s="17">
-        <f>G23-J23</f>
-        <v>0</v>
-      </c>
-      <c r="L23" s="17">
-        <f>L22+K23</f>
-        <v>0</v>
+        <v>2035.0000000000002</v>
+      </c>
+      <c r="J23" s="13">
+        <f t="shared" si="1"/>
+        <v>4407</v>
+      </c>
+      <c r="K23" s="15">
+        <f t="shared" si="2"/>
+        <v>6436.0357142857138</v>
+      </c>
+      <c r="L23" s="15">
+        <f t="shared" si="4"/>
+        <v>43168.857142857145</v>
       </c>
     </row>
     <row r="24" spans="2:12" ht="20" customHeight="1">
-      <c r="B24" s="15">
+      <c r="B24" s="13">
         <v>18</v>
       </c>
-      <c r="C24" s="13">
+      <c r="C24" s="11">
         <v>3</v>
       </c>
-      <c r="D24" s="15">
-        <f>D23+C24</f>
-        <v>0</v>
-      </c>
-      <c r="E24" s="15">
+      <c r="D24" s="13">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="E24" s="13">
         <f>C24*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F24" s="13">
         <f>D24*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G24" s="12">
-        <f>E24+F24</f>
-        <v>0</v>
-      </c>
-      <c r="H24" s="15">
+        <v>7104.2000000000007</v>
+      </c>
+      <c r="G24" s="10">
+        <f t="shared" si="0"/>
+        <v>11604.2</v>
+      </c>
+      <c r="H24" s="13">
         <f>'Cost Inputs'!$C$13+IF(D24&gt;=10,'Cost Inputs'!$C$17,0)+IF(D24&gt;=20,'Cost Inputs'!$C$18,0)+IF(D24&gt;=30,'Cost Inputs'!$C$19,0)+IF(D24&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I24" s="15">
+        <v>2372</v>
+      </c>
+      <c r="I24" s="13">
         <f>IF(D24&lt;='Cost Inputs'!$C$28,D24*'Cost Inputs'!$C$26,D24*'Cost Inputs'!$C$27)+D24*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J24" s="15">
-        <f>H24+I24</f>
-        <v>0</v>
-      </c>
-      <c r="K24" s="17">
-        <f>G24-J24</f>
-        <v>0</v>
-      </c>
-      <c r="L24" s="17">
-        <f>L23+K24</f>
-        <v>0</v>
+        <v>2279.2000000000007</v>
+      </c>
+      <c r="J24" s="13">
+        <f t="shared" si="1"/>
+        <v>4651.2000000000007</v>
+      </c>
+      <c r="K24" s="15">
+        <f t="shared" si="2"/>
+        <v>6953</v>
+      </c>
+      <c r="L24" s="15">
+        <f t="shared" si="4"/>
+        <v>50121.857142857145</v>
       </c>
     </row>
     <row r="25" spans="2:12" ht="20" customHeight="1">
-      <c r="B25" s="15">
+      <c r="B25" s="13">
         <v>19</v>
       </c>
-      <c r="C25" s="13">
+      <c r="C25" s="11">
         <v>3</v>
       </c>
-      <c r="D25" s="15">
-        <f>D24+C25</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="15">
+      <c r="D25" s="13">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="E25" s="13">
         <f>C25*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="15">
+        <v>4500</v>
+      </c>
+      <c r="F25" s="13">
         <f>D25*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="12">
-        <f>E25+F25</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="15">
+        <v>7865.3642857142859</v>
+      </c>
+      <c r="G25" s="10">
+        <f t="shared" si="0"/>
+        <v>12365.364285714286</v>
+      </c>
+      <c r="H25" s="13">
         <f>'Cost Inputs'!$C$13+IF(D25&gt;=10,'Cost Inputs'!$C$17,0)+IF(D25&gt;=20,'Cost Inputs'!$C$18,0)+IF(D25&gt;=30,'Cost Inputs'!$C$19,0)+IF(D25&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="15">
+        <v>2622</v>
+      </c>
+      <c r="I25" s="13">
         <f>IF(D25&lt;='Cost Inputs'!$C$28,D25*'Cost Inputs'!$C$26,D25*'Cost Inputs'!$C$27)+D25*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J25" s="15">
-        <f>H25+I25</f>
-        <v>0</v>
-      </c>
-      <c r="K25" s="17">
-        <f>G25-J25</f>
-        <v>0</v>
-      </c>
-      <c r="L25" s="17">
-        <f>L24+K25</f>
-        <v>0</v>
+        <v>2523.4</v>
+      </c>
+      <c r="J25" s="13">
+        <f t="shared" si="1"/>
+        <v>5145.3999999999996</v>
+      </c>
+      <c r="K25" s="15">
+        <f t="shared" si="2"/>
+        <v>7219.9642857142862</v>
+      </c>
+      <c r="L25" s="15">
+        <f t="shared" si="4"/>
+        <v>57341.821428571435</v>
       </c>
     </row>
     <row r="26" spans="2:12" ht="20" customHeight="1">
-      <c r="B26" s="15">
+      <c r="B26" s="13">
         <v>20</v>
       </c>
-      <c r="C26" s="13">
+      <c r="C26" s="11">
         <v>4</v>
       </c>
-      <c r="D26" s="15">
-        <f>D25+C26</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="15">
+      <c r="D26" s="13">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="E26" s="13">
         <f>C26*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="15">
+        <v>6000</v>
+      </c>
+      <c r="F26" s="13">
         <f>D26*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G26" s="12">
-        <f>E26+F26</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="15">
+        <v>8880.25</v>
+      </c>
+      <c r="G26" s="10">
+        <f t="shared" si="0"/>
+        <v>14880.25</v>
+      </c>
+      <c r="H26" s="13">
         <f>'Cost Inputs'!$C$13+IF(D26&gt;=10,'Cost Inputs'!$C$17,0)+IF(D26&gt;=20,'Cost Inputs'!$C$18,0)+IF(D26&gt;=30,'Cost Inputs'!$C$19,0)+IF(D26&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="15">
+        <v>2622</v>
+      </c>
+      <c r="I26" s="13">
         <f>IF(D26&lt;='Cost Inputs'!$C$28,D26*'Cost Inputs'!$C$26,D26*'Cost Inputs'!$C$27)+D26*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J26" s="15">
-        <f>H26+I26</f>
-        <v>0</v>
-      </c>
-      <c r="K26" s="17">
-        <f>G26-J26</f>
-        <v>0</v>
-      </c>
-      <c r="L26" s="17">
-        <f>L25+K26</f>
-        <v>0</v>
+        <v>2849.0000000000005</v>
+      </c>
+      <c r="J26" s="13">
+        <f t="shared" si="1"/>
+        <v>5471</v>
+      </c>
+      <c r="K26" s="15">
+        <f t="shared" si="2"/>
+        <v>9409.25</v>
+      </c>
+      <c r="L26" s="15">
+        <f t="shared" si="4"/>
+        <v>66751.071428571435</v>
       </c>
     </row>
     <row r="27" spans="2:12" ht="20" customHeight="1">
-      <c r="B27" s="15">
+      <c r="B27" s="13">
         <v>21</v>
       </c>
-      <c r="C27" s="13">
+      <c r="C27" s="11">
         <v>4</v>
       </c>
-      <c r="D27" s="15">
-        <f>D26+C27</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="15">
+      <c r="D27" s="13">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="E27" s="13">
         <f>C27*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F27" s="15">
+        <v>6000</v>
+      </c>
+      <c r="F27" s="13">
         <f>D27*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G27" s="12">
-        <f>E27+F27</f>
-        <v>0</v>
-      </c>
-      <c r="H27" s="15">
+        <v>9895.1357142857141</v>
+      </c>
+      <c r="G27" s="10">
+        <f t="shared" si="0"/>
+        <v>15895.135714285714</v>
+      </c>
+      <c r="H27" s="13">
         <f>'Cost Inputs'!$C$13+IF(D27&gt;=10,'Cost Inputs'!$C$17,0)+IF(D27&gt;=20,'Cost Inputs'!$C$18,0)+IF(D27&gt;=30,'Cost Inputs'!$C$19,0)+IF(D27&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I27" s="15">
+        <v>2622</v>
+      </c>
+      <c r="I27" s="13">
         <f>IF(D27&lt;='Cost Inputs'!$C$28,D27*'Cost Inputs'!$C$26,D27*'Cost Inputs'!$C$27)+D27*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J27" s="15">
-        <f>H27+I27</f>
-        <v>0</v>
-      </c>
-      <c r="K27" s="17">
-        <f>G27-J27</f>
-        <v>0</v>
-      </c>
-      <c r="L27" s="17">
-        <f>L26+K27</f>
-        <v>0</v>
+        <v>3174.6000000000004</v>
+      </c>
+      <c r="J27" s="13">
+        <f t="shared" si="1"/>
+        <v>5796.6</v>
+      </c>
+      <c r="K27" s="15">
+        <f t="shared" si="2"/>
+        <v>10098.535714285714</v>
+      </c>
+      <c r="L27" s="15">
+        <f t="shared" si="4"/>
+        <v>76849.607142857145</v>
       </c>
     </row>
     <row r="28" spans="2:12" ht="20" customHeight="1">
-      <c r="B28" s="15">
+      <c r="B28" s="13">
         <v>22</v>
       </c>
-      <c r="C28" s="13">
+      <c r="C28" s="11">
         <v>4</v>
       </c>
-      <c r="D28" s="15">
-        <f>D27+C28</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="15">
+      <c r="D28" s="13">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="E28" s="13">
         <f>C28*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F28" s="15">
+        <v>6000</v>
+      </c>
+      <c r="F28" s="13">
         <f>D28*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G28" s="12">
-        <f>E28+F28</f>
-        <v>0</v>
-      </c>
-      <c r="H28" s="15">
+        <v>10910.02142857143</v>
+      </c>
+      <c r="G28" s="10">
+        <f t="shared" si="0"/>
+        <v>16910.021428571432</v>
+      </c>
+      <c r="H28" s="13">
         <f>'Cost Inputs'!$C$13+IF(D28&gt;=10,'Cost Inputs'!$C$17,0)+IF(D28&gt;=20,'Cost Inputs'!$C$18,0)+IF(D28&gt;=30,'Cost Inputs'!$C$19,0)+IF(D28&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="15">
+        <v>2622</v>
+      </c>
+      <c r="I28" s="13">
         <f>IF(D28&lt;='Cost Inputs'!$C$28,D28*'Cost Inputs'!$C$26,D28*'Cost Inputs'!$C$27)+D28*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J28" s="15">
-        <f>H28+I28</f>
-        <v>0</v>
-      </c>
-      <c r="K28" s="17">
-        <f>G28-J28</f>
-        <v>0</v>
-      </c>
-      <c r="L28" s="17">
-        <f>L27+K28</f>
-        <v>0</v>
+        <v>3500.2000000000007</v>
+      </c>
+      <c r="J28" s="13">
+        <f t="shared" si="1"/>
+        <v>6122.2000000000007</v>
+      </c>
+      <c r="K28" s="15">
+        <f t="shared" si="2"/>
+        <v>10787.821428571431</v>
+      </c>
+      <c r="L28" s="15">
+        <f t="shared" si="4"/>
+        <v>87637.42857142858</v>
       </c>
     </row>
     <row r="29" spans="2:12" ht="20" customHeight="1">
-      <c r="B29" s="15">
+      <c r="B29" s="13">
         <v>23</v>
       </c>
-      <c r="C29" s="13">
+      <c r="C29" s="11">
         <v>4</v>
       </c>
-      <c r="D29" s="15">
-        <f>D28+C29</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="15">
+      <c r="D29" s="13">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E29" s="13">
         <f>C29*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F29" s="15">
+        <v>6000</v>
+      </c>
+      <c r="F29" s="13">
         <f>D29*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G29" s="12">
-        <f>E29+F29</f>
-        <v>0</v>
-      </c>
-      <c r="H29" s="15">
+        <v>11924.907142857144</v>
+      </c>
+      <c r="G29" s="10">
+        <f t="shared" si="0"/>
+        <v>17924.907142857144</v>
+      </c>
+      <c r="H29" s="13">
         <f>'Cost Inputs'!$C$13+IF(D29&gt;=10,'Cost Inputs'!$C$17,0)+IF(D29&gt;=20,'Cost Inputs'!$C$18,0)+IF(D29&gt;=30,'Cost Inputs'!$C$19,0)+IF(D29&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I29" s="15">
+        <v>2622</v>
+      </c>
+      <c r="I29" s="13">
         <f>IF(D29&lt;='Cost Inputs'!$C$28,D29*'Cost Inputs'!$C$26,D29*'Cost Inputs'!$C$27)+D29*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J29" s="15">
-        <f>H29+I29</f>
-        <v>0</v>
-      </c>
-      <c r="K29" s="17">
-        <f>G29-J29</f>
-        <v>0</v>
-      </c>
-      <c r="L29" s="17">
-        <f>L28+K29</f>
-        <v>0</v>
+        <v>3825.8</v>
+      </c>
+      <c r="J29" s="13">
+        <f t="shared" si="1"/>
+        <v>6447.8</v>
+      </c>
+      <c r="K29" s="15">
+        <f t="shared" si="2"/>
+        <v>11477.107142857145</v>
+      </c>
+      <c r="L29" s="15">
+        <f t="shared" si="4"/>
+        <v>99114.535714285725</v>
       </c>
     </row>
     <row r="30" spans="2:12" ht="20" customHeight="1">
-      <c r="B30" s="15">
+      <c r="B30" s="13">
         <v>24</v>
       </c>
-      <c r="C30" s="13">
+      <c r="C30" s="11">
         <v>4</v>
       </c>
-      <c r="D30" s="15">
-        <f>D29+C30</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="15">
+      <c r="D30" s="13">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="E30" s="13">
         <f>C30*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="15">
+        <v>6000</v>
+      </c>
+      <c r="F30" s="13">
         <f>D30*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G30" s="12">
-        <f>E30+F30</f>
-        <v>0</v>
-      </c>
-      <c r="H30" s="15">
+        <v>12939.792857142858</v>
+      </c>
+      <c r="G30" s="10">
+        <f t="shared" si="0"/>
+        <v>18939.792857142857</v>
+      </c>
+      <c r="H30" s="13">
         <f>'Cost Inputs'!$C$13+IF(D30&gt;=10,'Cost Inputs'!$C$17,0)+IF(D30&gt;=20,'Cost Inputs'!$C$18,0)+IF(D30&gt;=30,'Cost Inputs'!$C$19,0)+IF(D30&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I30" s="15">
+        <v>2622</v>
+      </c>
+      <c r="I30" s="13">
         <f>IF(D30&lt;='Cost Inputs'!$C$28,D30*'Cost Inputs'!$C$26,D30*'Cost Inputs'!$C$27)+D30*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J30" s="15">
-        <f>H30+I30</f>
-        <v>0</v>
-      </c>
-      <c r="K30" s="17">
-        <f>G30-J30</f>
-        <v>0</v>
-      </c>
-      <c r="L30" s="17">
-        <f>L29+K30</f>
-        <v>0</v>
+        <v>4151.4000000000005</v>
+      </c>
+      <c r="J30" s="13">
+        <f t="shared" si="1"/>
+        <v>6773.4000000000005</v>
+      </c>
+      <c r="K30" s="15">
+        <f t="shared" si="2"/>
+        <v>12166.392857142855</v>
+      </c>
+      <c r="L30" s="15">
+        <f t="shared" si="4"/>
+        <v>111280.92857142858</v>
       </c>
     </row>
     <row r="31" spans="2:12" ht="20" customHeight="1">
-      <c r="B31" s="15">
+      <c r="B31" s="13">
         <v>25</v>
       </c>
-      <c r="C31" s="13">
+      <c r="C31" s="11">
         <v>5</v>
       </c>
-      <c r="D31" s="15">
-        <f>D30+C31</f>
-        <v>0</v>
-      </c>
-      <c r="E31" s="15">
+      <c r="D31" s="13">
+        <f t="shared" si="3"/>
+        <v>56</v>
+      </c>
+      <c r="E31" s="13">
         <f>C31*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="15">
+        <v>7500</v>
+      </c>
+      <c r="F31" s="13">
         <f>D31*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G31" s="12">
-        <f>E31+F31</f>
-        <v>0</v>
-      </c>
-      <c r="H31" s="15">
+        <v>14208.400000000001</v>
+      </c>
+      <c r="G31" s="10">
+        <f t="shared" si="0"/>
+        <v>21708.400000000001</v>
+      </c>
+      <c r="H31" s="13">
         <f>'Cost Inputs'!$C$13+IF(D31&gt;=10,'Cost Inputs'!$C$17,0)+IF(D31&gt;=20,'Cost Inputs'!$C$18,0)+IF(D31&gt;=30,'Cost Inputs'!$C$19,0)+IF(D31&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I31" s="15">
+        <v>2622</v>
+      </c>
+      <c r="I31" s="13">
         <f>IF(D31&lt;='Cost Inputs'!$C$28,D31*'Cost Inputs'!$C$26,D31*'Cost Inputs'!$C$27)+D31*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J31" s="15">
-        <f>H31+I31</f>
-        <v>0</v>
-      </c>
-      <c r="K31" s="17">
-        <f>G31-J31</f>
-        <v>0</v>
-      </c>
-      <c r="L31" s="17">
-        <f>L30+K31</f>
-        <v>0</v>
+        <v>4558.4000000000015</v>
+      </c>
+      <c r="J31" s="13">
+        <f t="shared" si="1"/>
+        <v>7180.4000000000015</v>
+      </c>
+      <c r="K31" s="15">
+        <f t="shared" si="2"/>
+        <v>14528</v>
+      </c>
+      <c r="L31" s="15">
+        <f t="shared" si="4"/>
+        <v>125808.92857142858</v>
       </c>
     </row>
     <row r="32" spans="2:12" ht="20" customHeight="1">
-      <c r="B32" s="15">
+      <c r="B32" s="13">
         <v>26</v>
       </c>
-      <c r="C32" s="13">
+      <c r="C32" s="11">
         <v>5</v>
       </c>
-      <c r="D32" s="15">
-        <f>D31+C32</f>
-        <v>0</v>
-      </c>
-      <c r="E32" s="15">
+      <c r="D32" s="13">
+        <f t="shared" si="3"/>
+        <v>61</v>
+      </c>
+      <c r="E32" s="13">
         <f>C32*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F32" s="15">
+        <v>7500</v>
+      </c>
+      <c r="F32" s="13">
         <f>D32*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G32" s="12">
-        <f>E32+F32</f>
-        <v>0</v>
-      </c>
-      <c r="H32" s="15">
+        <v>15477.007142857145</v>
+      </c>
+      <c r="G32" s="10">
+        <f t="shared" si="0"/>
+        <v>22977.007142857146</v>
+      </c>
+      <c r="H32" s="13">
         <f>'Cost Inputs'!$C$13+IF(D32&gt;=10,'Cost Inputs'!$C$17,0)+IF(D32&gt;=20,'Cost Inputs'!$C$18,0)+IF(D32&gt;=30,'Cost Inputs'!$C$19,0)+IF(D32&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I32" s="15">
+        <v>2622</v>
+      </c>
+      <c r="I32" s="13">
         <f>IF(D32&lt;='Cost Inputs'!$C$28,D32*'Cost Inputs'!$C$26,D32*'Cost Inputs'!$C$27)+D32*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J32" s="15">
-        <f>H32+I32</f>
-        <v>0</v>
-      </c>
-      <c r="K32" s="17">
-        <f>G32-J32</f>
-        <v>0</v>
-      </c>
-      <c r="L32" s="17">
-        <f>L31+K32</f>
-        <v>0</v>
+        <v>4965.4000000000015</v>
+      </c>
+      <c r="J32" s="13">
+        <f t="shared" si="1"/>
+        <v>7587.4000000000015</v>
+      </c>
+      <c r="K32" s="15">
+        <f t="shared" si="2"/>
+        <v>15389.607142857145</v>
+      </c>
+      <c r="L32" s="15">
+        <f t="shared" si="4"/>
+        <v>141198.53571428574</v>
       </c>
     </row>
     <row r="33" spans="2:12" ht="20" customHeight="1">
-      <c r="B33" s="15">
+      <c r="B33" s="13">
         <v>27</v>
       </c>
-      <c r="C33" s="13">
+      <c r="C33" s="11">
         <v>5</v>
       </c>
-      <c r="D33" s="15">
-        <f>D32+C33</f>
-        <v>0</v>
-      </c>
-      <c r="E33" s="15">
+      <c r="D33" s="13">
+        <f t="shared" si="3"/>
+        <v>66</v>
+      </c>
+      <c r="E33" s="13">
         <f>C33*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="15">
+        <v>7500</v>
+      </c>
+      <c r="F33" s="13">
         <f>D33*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G33" s="12">
-        <f>E33+F33</f>
-        <v>0</v>
-      </c>
-      <c r="H33" s="15">
+        <v>16745.614285714288</v>
+      </c>
+      <c r="G33" s="10">
+        <f t="shared" si="0"/>
+        <v>24245.614285714288</v>
+      </c>
+      <c r="H33" s="13">
         <f>'Cost Inputs'!$C$13+IF(D33&gt;=10,'Cost Inputs'!$C$17,0)+IF(D33&gt;=20,'Cost Inputs'!$C$18,0)+IF(D33&gt;=30,'Cost Inputs'!$C$19,0)+IF(D33&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I33" s="15">
+        <v>2622</v>
+      </c>
+      <c r="I33" s="13">
         <f>IF(D33&lt;='Cost Inputs'!$C$28,D33*'Cost Inputs'!$C$26,D33*'Cost Inputs'!$C$27)+D33*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="15">
-        <f>H33+I33</f>
-        <v>0</v>
-      </c>
-      <c r="K33" s="17">
-        <f>G33-J33</f>
-        <v>0</v>
-      </c>
-      <c r="L33" s="17">
-        <f>L32+K33</f>
-        <v>0</v>
+        <v>5372.4000000000015</v>
+      </c>
+      <c r="J33" s="13">
+        <f t="shared" si="1"/>
+        <v>7994.4000000000015</v>
+      </c>
+      <c r="K33" s="15">
+        <f t="shared" si="2"/>
+        <v>16251.214285714286</v>
+      </c>
+      <c r="L33" s="15">
+        <f t="shared" si="4"/>
+        <v>157449.75000000003</v>
       </c>
     </row>
     <row r="34" spans="2:12" ht="20" customHeight="1">
-      <c r="B34" s="15">
+      <c r="B34" s="13">
         <v>28</v>
       </c>
-      <c r="C34" s="13">
+      <c r="C34" s="11">
         <v>5</v>
       </c>
-      <c r="D34" s="15">
-        <f>D33+C34</f>
-        <v>0</v>
-      </c>
-      <c r="E34" s="15">
+      <c r="D34" s="13">
+        <f t="shared" si="3"/>
+        <v>71</v>
+      </c>
+      <c r="E34" s="13">
         <f>C34*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F34" s="15">
+        <v>7500</v>
+      </c>
+      <c r="F34" s="13">
         <f>D34*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G34" s="12">
-        <f>E34+F34</f>
-        <v>0</v>
-      </c>
-      <c r="H34" s="15">
+        <v>18014.221428571429</v>
+      </c>
+      <c r="G34" s="10">
+        <f t="shared" si="0"/>
+        <v>25514.221428571429</v>
+      </c>
+      <c r="H34" s="13">
         <f>'Cost Inputs'!$C$13+IF(D34&gt;=10,'Cost Inputs'!$C$17,0)+IF(D34&gt;=20,'Cost Inputs'!$C$18,0)+IF(D34&gt;=30,'Cost Inputs'!$C$19,0)+IF(D34&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I34" s="15">
+        <v>2622</v>
+      </c>
+      <c r="I34" s="13">
         <f>IF(D34&lt;='Cost Inputs'!$C$28,D34*'Cost Inputs'!$C$26,D34*'Cost Inputs'!$C$27)+D34*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J34" s="15">
-        <f>H34+I34</f>
-        <v>0</v>
-      </c>
-      <c r="K34" s="17">
-        <f>G34-J34</f>
-        <v>0</v>
-      </c>
-      <c r="L34" s="17">
-        <f>L33+K34</f>
-        <v>0</v>
+        <v>5779.4000000000015</v>
+      </c>
+      <c r="J34" s="13">
+        <f t="shared" si="1"/>
+        <v>8401.4000000000015</v>
+      </c>
+      <c r="K34" s="15">
+        <f t="shared" si="2"/>
+        <v>17112.821428571428</v>
+      </c>
+      <c r="L34" s="15">
+        <f t="shared" si="4"/>
+        <v>174562.57142857145</v>
       </c>
     </row>
     <row r="35" spans="2:12" ht="20" customHeight="1">
-      <c r="B35" s="15">
+      <c r="B35" s="13">
         <v>29</v>
       </c>
-      <c r="C35" s="13">
+      <c r="C35" s="11">
         <v>5</v>
       </c>
-      <c r="D35" s="15">
-        <f>D34+C35</f>
-        <v>0</v>
-      </c>
-      <c r="E35" s="15">
+      <c r="D35" s="13">
+        <f t="shared" si="3"/>
+        <v>76</v>
+      </c>
+      <c r="E35" s="13">
         <f>C35*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F35" s="15">
+        <v>7500</v>
+      </c>
+      <c r="F35" s="13">
         <f>D35*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G35" s="12">
-        <f>E35+F35</f>
-        <v>0</v>
-      </c>
-      <c r="H35" s="15">
+        <v>19282.828571428574</v>
+      </c>
+      <c r="G35" s="10">
+        <f t="shared" si="0"/>
+        <v>26782.828571428574</v>
+      </c>
+      <c r="H35" s="13">
         <f>'Cost Inputs'!$C$13+IF(D35&gt;=10,'Cost Inputs'!$C$17,0)+IF(D35&gt;=20,'Cost Inputs'!$C$18,0)+IF(D35&gt;=30,'Cost Inputs'!$C$19,0)+IF(D35&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I35" s="15">
+        <v>2622</v>
+      </c>
+      <c r="I35" s="13">
         <f>IF(D35&lt;='Cost Inputs'!$C$28,D35*'Cost Inputs'!$C$26,D35*'Cost Inputs'!$C$27)+D35*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J35" s="15">
-        <f>H35+I35</f>
-        <v>0</v>
-      </c>
-      <c r="K35" s="17">
-        <f>G35-J35</f>
-        <v>0</v>
-      </c>
-      <c r="L35" s="17">
-        <f>L34+K35</f>
-        <v>0</v>
+        <v>6186.4000000000015</v>
+      </c>
+      <c r="J35" s="13">
+        <f t="shared" si="1"/>
+        <v>8808.4000000000015</v>
+      </c>
+      <c r="K35" s="15">
+        <f t="shared" si="2"/>
+        <v>17974.428571428572</v>
+      </c>
+      <c r="L35" s="15">
+        <f t="shared" si="4"/>
+        <v>192537.00000000003</v>
       </c>
     </row>
     <row r="36" spans="2:12" ht="20" customHeight="1">
-      <c r="B36" s="15">
+      <c r="B36" s="13">
         <v>30</v>
       </c>
-      <c r="C36" s="13">
+      <c r="C36" s="11">
         <v>5</v>
       </c>
-      <c r="D36" s="15">
-        <f>D35+C36</f>
-        <v>0</v>
-      </c>
-      <c r="E36" s="15">
+      <c r="D36" s="13">
+        <f t="shared" si="3"/>
+        <v>81</v>
+      </c>
+      <c r="E36" s="13">
         <f>C36*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F36" s="15">
+        <v>7500</v>
+      </c>
+      <c r="F36" s="13">
         <f>D36*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G36" s="12">
-        <f>E36+F36</f>
-        <v>0</v>
-      </c>
-      <c r="H36" s="15">
+        <v>20551.435714285715</v>
+      </c>
+      <c r="G36" s="10">
+        <f t="shared" si="0"/>
+        <v>28051.435714285715</v>
+      </c>
+      <c r="H36" s="13">
         <f>'Cost Inputs'!$C$13+IF(D36&gt;=10,'Cost Inputs'!$C$17,0)+IF(D36&gt;=20,'Cost Inputs'!$C$18,0)+IF(D36&gt;=30,'Cost Inputs'!$C$19,0)+IF(D36&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I36" s="15">
+        <v>2622</v>
+      </c>
+      <c r="I36" s="13">
         <f>IF(D36&lt;='Cost Inputs'!$C$28,D36*'Cost Inputs'!$C$26,D36*'Cost Inputs'!$C$27)+D36*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J36" s="15">
-        <f>H36+I36</f>
-        <v>0</v>
-      </c>
-      <c r="K36" s="17">
-        <f>G36-J36</f>
-        <v>0</v>
-      </c>
-      <c r="L36" s="17">
-        <f>L35+K36</f>
-        <v>0</v>
+        <v>6593.4000000000015</v>
+      </c>
+      <c r="J36" s="13">
+        <f t="shared" si="1"/>
+        <v>9215.4000000000015</v>
+      </c>
+      <c r="K36" s="15">
+        <f t="shared" si="2"/>
+        <v>18836.035714285714</v>
+      </c>
+      <c r="L36" s="15">
+        <f t="shared" si="4"/>
+        <v>211373.03571428574</v>
       </c>
     </row>
     <row r="37" spans="2:12" ht="20" customHeight="1">
-      <c r="B37" s="15">
+      <c r="B37" s="13">
         <v>31</v>
       </c>
-      <c r="C37" s="13">
+      <c r="C37" s="11">
         <v>6</v>
       </c>
-      <c r="D37" s="15">
-        <f>D36+C37</f>
-        <v>0</v>
-      </c>
-      <c r="E37" s="15">
+      <c r="D37" s="13">
+        <f t="shared" si="3"/>
+        <v>87</v>
+      </c>
+      <c r="E37" s="13">
         <f>C37*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F37" s="15">
+        <v>9000</v>
+      </c>
+      <c r="F37" s="13">
         <f>D37*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G37" s="12">
-        <f>E37+F37</f>
-        <v>0</v>
-      </c>
-      <c r="H37" s="15">
+        <v>22073.764285714286</v>
+      </c>
+      <c r="G37" s="10">
+        <f t="shared" si="0"/>
+        <v>31073.764285714286</v>
+      </c>
+      <c r="H37" s="13">
         <f>'Cost Inputs'!$C$13+IF(D37&gt;=10,'Cost Inputs'!$C$17,0)+IF(D37&gt;=20,'Cost Inputs'!$C$18,0)+IF(D37&gt;=30,'Cost Inputs'!$C$19,0)+IF(D37&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I37" s="15">
+        <v>2622</v>
+      </c>
+      <c r="I37" s="13">
         <f>IF(D37&lt;='Cost Inputs'!$C$28,D37*'Cost Inputs'!$C$26,D37*'Cost Inputs'!$C$27)+D37*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J37" s="15">
-        <f>H37+I37</f>
-        <v>0</v>
-      </c>
-      <c r="K37" s="17">
-        <f>G37-J37</f>
-        <v>0</v>
-      </c>
-      <c r="L37" s="17">
-        <f>L36+K37</f>
-        <v>0</v>
+        <v>7081.8000000000011</v>
+      </c>
+      <c r="J37" s="13">
+        <f t="shared" si="1"/>
+        <v>9703.8000000000011</v>
+      </c>
+      <c r="K37" s="15">
+        <f t="shared" si="2"/>
+        <v>21369.964285714283</v>
+      </c>
+      <c r="L37" s="15">
+        <f t="shared" si="4"/>
+        <v>232743.00000000003</v>
       </c>
     </row>
     <row r="38" spans="2:12" ht="20" customHeight="1">
-      <c r="B38" s="15">
-        <v>32</v>
-      </c>
-      <c r="C38" s="13">
+      <c r="B38" s="13">
+        <v>32</v>
+      </c>
+      <c r="C38" s="11">
         <v>6</v>
       </c>
-      <c r="D38" s="15">
-        <f>D37+C38</f>
-        <v>0</v>
-      </c>
-      <c r="E38" s="15">
+      <c r="D38" s="13">
+        <f t="shared" si="3"/>
+        <v>93</v>
+      </c>
+      <c r="E38" s="13">
         <f>C38*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F38" s="15">
+        <v>9000</v>
+      </c>
+      <c r="F38" s="13">
         <f>D38*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G38" s="12">
-        <f>E38+F38</f>
-        <v>0</v>
-      </c>
-      <c r="H38" s="15">
+        <v>23596.092857142859</v>
+      </c>
+      <c r="G38" s="10">
+        <f t="shared" si="0"/>
+        <v>32596.092857142859</v>
+      </c>
+      <c r="H38" s="13">
         <f>'Cost Inputs'!$C$13+IF(D38&gt;=10,'Cost Inputs'!$C$17,0)+IF(D38&gt;=20,'Cost Inputs'!$C$18,0)+IF(D38&gt;=30,'Cost Inputs'!$C$19,0)+IF(D38&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I38" s="15">
+        <v>2622</v>
+      </c>
+      <c r="I38" s="13">
         <f>IF(D38&lt;='Cost Inputs'!$C$28,D38*'Cost Inputs'!$C$26,D38*'Cost Inputs'!$C$27)+D38*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J38" s="15">
-        <f>H38+I38</f>
-        <v>0</v>
-      </c>
-      <c r="K38" s="17">
-        <f>G38-J38</f>
-        <v>0</v>
-      </c>
-      <c r="L38" s="17">
-        <f>L37+K38</f>
-        <v>0</v>
+        <v>7570.2000000000016</v>
+      </c>
+      <c r="J38" s="13">
+        <f t="shared" si="1"/>
+        <v>10192.200000000001</v>
+      </c>
+      <c r="K38" s="15">
+        <f t="shared" si="2"/>
+        <v>22403.892857142859</v>
+      </c>
+      <c r="L38" s="15">
+        <f t="shared" si="4"/>
+        <v>255146.8928571429</v>
       </c>
     </row>
     <row r="39" spans="2:12" ht="20" customHeight="1">
-      <c r="B39" s="15">
+      <c r="B39" s="13">
         <v>33</v>
       </c>
-      <c r="C39" s="13">
+      <c r="C39" s="11">
         <v>6</v>
       </c>
-      <c r="D39" s="15">
-        <f>D38+C39</f>
-        <v>0</v>
-      </c>
-      <c r="E39" s="15">
+      <c r="D39" s="13">
+        <f t="shared" si="3"/>
+        <v>99</v>
+      </c>
+      <c r="E39" s="13">
         <f>C39*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F39" s="15">
+        <v>9000</v>
+      </c>
+      <c r="F39" s="13">
         <f>D39*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G39" s="12">
-        <f>E39+F39</f>
-        <v>0</v>
-      </c>
-      <c r="H39" s="15">
+        <v>25118.42142857143</v>
+      </c>
+      <c r="G39" s="10">
+        <f t="shared" si="0"/>
+        <v>34118.421428571426</v>
+      </c>
+      <c r="H39" s="13">
         <f>'Cost Inputs'!$C$13+IF(D39&gt;=10,'Cost Inputs'!$C$17,0)+IF(D39&gt;=20,'Cost Inputs'!$C$18,0)+IF(D39&gt;=30,'Cost Inputs'!$C$19,0)+IF(D39&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I39" s="15">
+        <v>2622</v>
+      </c>
+      <c r="I39" s="13">
         <f>IF(D39&lt;='Cost Inputs'!$C$28,D39*'Cost Inputs'!$C$26,D39*'Cost Inputs'!$C$27)+D39*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J39" s="15">
-        <f>H39+I39</f>
-        <v>0</v>
-      </c>
-      <c r="K39" s="17">
-        <f>G39-J39</f>
-        <v>0</v>
-      </c>
-      <c r="L39" s="17">
-        <f>L38+K39</f>
-        <v>0</v>
+        <v>8058.6</v>
+      </c>
+      <c r="J39" s="13">
+        <f t="shared" si="1"/>
+        <v>10680.6</v>
+      </c>
+      <c r="K39" s="15">
+        <f t="shared" si="2"/>
+        <v>23437.821428571428</v>
+      </c>
+      <c r="L39" s="15">
+        <f t="shared" si="4"/>
+        <v>278584.71428571432</v>
       </c>
     </row>
     <row r="40" spans="2:12" ht="20" customHeight="1">
-      <c r="B40" s="15">
+      <c r="B40" s="13">
         <v>34</v>
       </c>
-      <c r="C40" s="13">
+      <c r="C40" s="11">
         <v>6</v>
       </c>
-      <c r="D40" s="15">
-        <f>D39+C40</f>
-        <v>0</v>
-      </c>
-      <c r="E40" s="15">
+      <c r="D40" s="13">
+        <f t="shared" si="3"/>
+        <v>105</v>
+      </c>
+      <c r="E40" s="13">
         <f>C40*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F40" s="15">
+        <v>9000</v>
+      </c>
+      <c r="F40" s="13">
         <f>D40*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G40" s="12">
-        <f>E40+F40</f>
-        <v>0</v>
-      </c>
-      <c r="H40" s="15">
+        <v>26640.750000000004</v>
+      </c>
+      <c r="G40" s="10">
+        <f t="shared" si="0"/>
+        <v>35640.75</v>
+      </c>
+      <c r="H40" s="13">
         <f>'Cost Inputs'!$C$13+IF(D40&gt;=10,'Cost Inputs'!$C$17,0)+IF(D40&gt;=20,'Cost Inputs'!$C$18,0)+IF(D40&gt;=30,'Cost Inputs'!$C$19,0)+IF(D40&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I40" s="15">
+        <v>2622</v>
+      </c>
+      <c r="I40" s="13">
         <f>IF(D40&lt;='Cost Inputs'!$C$28,D40*'Cost Inputs'!$C$26,D40*'Cost Inputs'!$C$27)+D40*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J40" s="15">
-        <f>H40+I40</f>
-        <v>0</v>
-      </c>
-      <c r="K40" s="17">
-        <f>G40-J40</f>
-        <v>0</v>
-      </c>
-      <c r="L40" s="17">
-        <f>L39+K40</f>
-        <v>0</v>
+        <v>8547</v>
+      </c>
+      <c r="J40" s="13">
+        <f t="shared" si="1"/>
+        <v>11169</v>
+      </c>
+      <c r="K40" s="15">
+        <f t="shared" si="2"/>
+        <v>24471.75</v>
+      </c>
+      <c r="L40" s="15">
+        <f t="shared" si="4"/>
+        <v>303056.46428571432</v>
       </c>
     </row>
     <row r="41" spans="2:12" ht="20" customHeight="1">
-      <c r="B41" s="15">
+      <c r="B41" s="13">
         <v>35</v>
       </c>
-      <c r="C41" s="13">
+      <c r="C41" s="11">
         <v>6</v>
       </c>
-      <c r="D41" s="15">
-        <f>D40+C41</f>
-        <v>0</v>
-      </c>
-      <c r="E41" s="15">
+      <c r="D41" s="13">
+        <f t="shared" si="3"/>
+        <v>111</v>
+      </c>
+      <c r="E41" s="13">
         <f>C41*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F41" s="15">
+        <v>9000</v>
+      </c>
+      <c r="F41" s="13">
         <f>D41*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G41" s="12">
-        <f>E41+F41</f>
-        <v>0</v>
-      </c>
-      <c r="H41" s="15">
+        <v>28163.078571428574</v>
+      </c>
+      <c r="G41" s="10">
+        <f t="shared" si="0"/>
+        <v>37163.078571428574</v>
+      </c>
+      <c r="H41" s="13">
         <f>'Cost Inputs'!$C$13+IF(D41&gt;=10,'Cost Inputs'!$C$17,0)+IF(D41&gt;=20,'Cost Inputs'!$C$18,0)+IF(D41&gt;=30,'Cost Inputs'!$C$19,0)+IF(D41&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I41" s="15">
+        <v>2622</v>
+      </c>
+      <c r="I41" s="13">
         <f>IF(D41&lt;='Cost Inputs'!$C$28,D41*'Cost Inputs'!$C$26,D41*'Cost Inputs'!$C$27)+D41*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J41" s="15">
-        <f>H41+I41</f>
-        <v>0</v>
-      </c>
-      <c r="K41" s="17">
-        <f>G41-J41</f>
-        <v>0</v>
-      </c>
-      <c r="L41" s="17">
-        <f>L40+K41</f>
-        <v>0</v>
+        <v>9035.4000000000015</v>
+      </c>
+      <c r="J41" s="13">
+        <f t="shared" si="1"/>
+        <v>11657.400000000001</v>
+      </c>
+      <c r="K41" s="15">
+        <f t="shared" si="2"/>
+        <v>25505.678571428572</v>
+      </c>
+      <c r="L41" s="15">
+        <f t="shared" si="4"/>
+        <v>328562.1428571429</v>
       </c>
     </row>
     <row r="42" spans="2:12" ht="20" customHeight="1">
-      <c r="B42" s="15">
+      <c r="B42" s="13">
         <v>36</v>
       </c>
-      <c r="C42" s="13">
+      <c r="C42" s="11">
         <v>6</v>
       </c>
-      <c r="D42" s="15">
-        <f>D41+C42</f>
-        <v>0</v>
-      </c>
-      <c r="E42" s="15">
+      <c r="D42" s="13">
+        <f t="shared" si="3"/>
+        <v>117</v>
+      </c>
+      <c r="E42" s="13">
         <f>C42*'Cost Inputs'!$C$44</f>
-        <v>0</v>
-      </c>
-      <c r="F42" s="15">
+        <v>9000</v>
+      </c>
+      <c r="F42" s="13">
         <f>D42*'Tier Pricing'!$E$23</f>
-        <v>0</v>
-      </c>
-      <c r="G42" s="12">
-        <f>E42+F42</f>
-        <v>0</v>
-      </c>
-      <c r="H42" s="15">
+        <v>29685.407142857144</v>
+      </c>
+      <c r="G42" s="10">
+        <f t="shared" si="0"/>
+        <v>38685.407142857148</v>
+      </c>
+      <c r="H42" s="13">
         <f>'Cost Inputs'!$C$13+IF(D42&gt;=10,'Cost Inputs'!$C$17,0)+IF(D42&gt;=20,'Cost Inputs'!$C$18,0)+IF(D42&gt;=30,'Cost Inputs'!$C$19,0)+IF(D42&gt;=20,'Cost Inputs'!$C$20,0)+0+0</f>
-        <v>0</v>
-      </c>
-      <c r="I42" s="15">
+        <v>2622</v>
+      </c>
+      <c r="I42" s="13">
         <f>IF(D42&lt;='Cost Inputs'!$C$28,D42*'Cost Inputs'!$C$26,D42*'Cost Inputs'!$C$27)+D42*'Tier Pricing'!$D$22*'Cost Inputs'!$C$40</f>
-        <v>0</v>
-      </c>
-      <c r="J42" s="15">
-        <f>H42+I42</f>
-        <v>0</v>
-      </c>
-      <c r="K42" s="17">
-        <f>G42-J42</f>
-        <v>0</v>
-      </c>
-      <c r="L42" s="17">
-        <f>L41+K42</f>
-        <v>0</v>
+        <v>9523.8000000000029</v>
+      </c>
+      <c r="J42" s="13">
+        <f t="shared" si="1"/>
+        <v>12145.800000000003</v>
+      </c>
+      <c r="K42" s="15">
+        <f t="shared" si="2"/>
+        <v>26539.607142857145</v>
+      </c>
+      <c r="L42" s="15">
+        <f t="shared" si="4"/>
+        <v>355101.75000000006</v>
       </c>
     </row>
     <row r="43" spans="2:12" ht="28" customHeight="1">
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="C43" s="12">
+      <c r="C43" s="10">
         <f>SUM(C7:C42)</f>
-        <v>0</v>
-      </c>
-      <c r="D43" s="15"/>
-      <c r="E43" s="12">
-        <f>SUM(E7:E42)</f>
-        <v>0</v>
-      </c>
-      <c r="F43" s="12">
-        <f>SUM(F7:F42)</f>
-        <v>0</v>
-      </c>
-      <c r="G43" s="12">
-        <f>SUM(G7:G42)</f>
-        <v>0</v>
-      </c>
-      <c r="H43" s="12">
-        <f>SUM(H7:H42)</f>
-        <v>0</v>
-      </c>
-      <c r="I43" s="12">
-        <f>SUM(I7:I42)</f>
-        <v>0</v>
-      </c>
-      <c r="J43" s="12">
-        <f>SUM(J7:J42)</f>
-        <v>0</v>
-      </c>
-      <c r="K43" s="12">
-        <f>SUM(K7:K42)</f>
-        <v>0</v>
-      </c>
-      <c r="L43" s="12">
+        <v>117</v>
+      </c>
+      <c r="D43" s="13"/>
+      <c r="E43" s="10">
+        <f t="shared" ref="E43:K43" si="5">SUM(E7:E42)</f>
+        <v>175500</v>
+      </c>
+      <c r="F43" s="10">
+        <f t="shared" si="5"/>
+        <v>367642.35000000003</v>
+      </c>
+      <c r="G43" s="10">
+        <f t="shared" si="5"/>
+        <v>543142.35000000009</v>
+      </c>
+      <c r="H43" s="10">
+        <f t="shared" si="5"/>
+        <v>68442</v>
+      </c>
+      <c r="I43" s="10">
+        <f t="shared" si="5"/>
+        <v>119598.60000000002</v>
+      </c>
+      <c r="J43" s="10">
+        <f t="shared" si="5"/>
+        <v>188040.59999999998</v>
+      </c>
+      <c r="K43" s="10">
+        <f t="shared" si="5"/>
+        <v>355101.75000000006</v>
+      </c>
+      <c r="L43" s="10">
         <f>L42</f>
-        <v>0</v>
+        <v>355101.75000000006</v>
       </c>
     </row>
   </sheetData>
@@ -5107,363 +5222,8 @@
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B3:L3"/>
   </mergeCells>
-  <conditionalFormatting sqref="K10">
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K11">
-    <cfRule type="cellIs" dxfId="0" priority="9" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K12">
-    <cfRule type="cellIs" dxfId="0" priority="11" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K13">
-    <cfRule type="cellIs" dxfId="0" priority="13" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K14">
-    <cfRule type="cellIs" dxfId="0" priority="15" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K15">
-    <cfRule type="cellIs" dxfId="0" priority="17" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K16">
-    <cfRule type="cellIs" dxfId="0" priority="19" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K17">
-    <cfRule type="cellIs" dxfId="0" priority="21" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K18">
-    <cfRule type="cellIs" dxfId="0" priority="23" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K19">
-    <cfRule type="cellIs" dxfId="0" priority="25" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K20">
-    <cfRule type="cellIs" dxfId="0" priority="27" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K21">
-    <cfRule type="cellIs" dxfId="0" priority="29" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K22">
-    <cfRule type="cellIs" dxfId="0" priority="31" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K23">
-    <cfRule type="cellIs" dxfId="0" priority="33" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K24">
-    <cfRule type="cellIs" dxfId="0" priority="35" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K25">
-    <cfRule type="cellIs" dxfId="0" priority="37" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K26">
-    <cfRule type="cellIs" dxfId="0" priority="39" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K27">
-    <cfRule type="cellIs" dxfId="0" priority="41" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K28">
-    <cfRule type="cellIs" dxfId="0" priority="43" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K29">
-    <cfRule type="cellIs" dxfId="0" priority="45" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K30">
-    <cfRule type="cellIs" dxfId="0" priority="47" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K31">
-    <cfRule type="cellIs" dxfId="0" priority="49" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K32">
-    <cfRule type="cellIs" dxfId="0" priority="51" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K33">
-    <cfRule type="cellIs" dxfId="0" priority="53" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K34">
-    <cfRule type="cellIs" dxfId="0" priority="55" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K35">
-    <cfRule type="cellIs" dxfId="0" priority="57" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K36">
-    <cfRule type="cellIs" dxfId="0" priority="59" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K37">
-    <cfRule type="cellIs" dxfId="0" priority="61" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K38">
-    <cfRule type="cellIs" dxfId="0" priority="63" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K39">
-    <cfRule type="cellIs" dxfId="0" priority="65" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K40">
-    <cfRule type="cellIs" dxfId="0" priority="67" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K41">
-    <cfRule type="cellIs" dxfId="0" priority="69" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K42">
-    <cfRule type="cellIs" dxfId="0" priority="71" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K7">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K8">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K9">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L10">
-    <cfRule type="cellIs" dxfId="0" priority="8" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L11">
-    <cfRule type="cellIs" dxfId="0" priority="10" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L12">
-    <cfRule type="cellIs" dxfId="0" priority="12" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L13">
-    <cfRule type="cellIs" dxfId="0" priority="14" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L14">
-    <cfRule type="cellIs" dxfId="0" priority="16" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L15">
-    <cfRule type="cellIs" dxfId="0" priority="18" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L16">
-    <cfRule type="cellIs" dxfId="0" priority="20" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L17">
-    <cfRule type="cellIs" dxfId="0" priority="22" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L18">
-    <cfRule type="cellIs" dxfId="0" priority="24" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L19">
-    <cfRule type="cellIs" dxfId="0" priority="26" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L20">
-    <cfRule type="cellIs" dxfId="0" priority="28" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L21">
-    <cfRule type="cellIs" dxfId="0" priority="30" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L22">
-    <cfRule type="cellIs" dxfId="0" priority="32" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L23">
-    <cfRule type="cellIs" dxfId="0" priority="34" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L24">
-    <cfRule type="cellIs" dxfId="0" priority="36" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L25">
-    <cfRule type="cellIs" dxfId="0" priority="38" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L26">
-    <cfRule type="cellIs" dxfId="0" priority="40" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L27">
-    <cfRule type="cellIs" dxfId="0" priority="42" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L28">
-    <cfRule type="cellIs" dxfId="0" priority="44" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L29">
-    <cfRule type="cellIs" dxfId="0" priority="46" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L30">
-    <cfRule type="cellIs" dxfId="0" priority="48" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L31">
-    <cfRule type="cellIs" dxfId="0" priority="50" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L32">
-    <cfRule type="cellIs" dxfId="0" priority="52" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L33">
-    <cfRule type="cellIs" dxfId="0" priority="54" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L34">
-    <cfRule type="cellIs" dxfId="0" priority="56" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L35">
-    <cfRule type="cellIs" dxfId="0" priority="58" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L36">
-    <cfRule type="cellIs" dxfId="0" priority="60" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L37">
-    <cfRule type="cellIs" dxfId="0" priority="62" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L38">
-    <cfRule type="cellIs" dxfId="0" priority="64" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L39">
-    <cfRule type="cellIs" dxfId="0" priority="66" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L40">
-    <cfRule type="cellIs" dxfId="0" priority="68" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L41">
-    <cfRule type="cellIs" dxfId="0" priority="70" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L42">
-    <cfRule type="cellIs" dxfId="0" priority="72" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L7">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L8">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L9">
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="lessThan">
+  <conditionalFormatting sqref="K7:L42">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5472,241 +5232,241 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor rgb="FF0D9488"/>
   </sheetPr>
   <dimension ref="B2:F21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
+    <col min="3" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="50.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="32" customHeight="1">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="18" t="s">
         <v>295</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
     </row>
     <row r="3" spans="2:6" ht="36" customHeight="1">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="19" t="s">
         <v>296</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
     </row>
     <row r="5" spans="2:6" ht="24" customHeight="1">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="16" t="s">
         <v>297</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
     </row>
     <row r="6" spans="2:6" ht="22" customHeight="1">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="5" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="24" customHeight="1">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="12">
         <v>0.5</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="24" customHeight="1">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="12">
         <v>0.5</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="22" customHeight="1">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="10">
         <f>SUM(C7:C8)</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="14" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="24" customHeight="1">
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="16" t="s">
         <v>308</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
     </row>
     <row r="12" spans="2:6" ht="22" customHeight="1">
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="5" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="26" customHeight="1">
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C13" s="12">
-        <f>SUM('Projection'!K7:K18)</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="12">
+      <c r="C13" s="10">
+        <f>SUM(Projection!K7:K18)</f>
+        <v>14936.000000000002</v>
+      </c>
+      <c r="D13" s="10">
         <f>C13*'Profit Split'!$C$7</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="12">
+        <v>7468.0000000000009</v>
+      </c>
+      <c r="E13" s="10">
         <f>C13*'Profit Split'!$C$8</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="4" t="s">
+        <v>7468.0000000000009</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="26" customHeight="1">
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="C14" s="12">
-        <f>SUM('Projection'!K19:K30)</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="12">
+      <c r="C14" s="10">
+        <f>SUM(Projection!K19:K30)</f>
+        <v>96344.92857142858</v>
+      </c>
+      <c r="D14" s="10">
         <f>C14*'Profit Split'!$C$7</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="12">
+        <v>48172.46428571429</v>
+      </c>
+      <c r="E14" s="10">
         <f>C14*'Profit Split'!$C$8</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="4"/>
+        <v>48172.46428571429</v>
+      </c>
+      <c r="F14" s="3"/>
     </row>
     <row r="15" spans="2:6" ht="26" customHeight="1">
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="C15" s="12">
-        <f>SUM('Projection'!K31:K42)</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="12">
+      <c r="C15" s="10">
+        <f>SUM(Projection!K31:K42)</f>
+        <v>243820.82142857142</v>
+      </c>
+      <c r="D15" s="10">
         <f>C15*'Profit Split'!$C$7</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="12">
+        <v>121910.41071428571</v>
+      </c>
+      <c r="E15" s="10">
         <f>C15*'Profit Split'!$C$8</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="4"/>
+        <v>121910.41071428571</v>
+      </c>
+      <c r="F15" s="3"/>
     </row>
     <row r="16" spans="2:6" ht="26" customHeight="1">
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="C16" s="12">
-        <f>SUM('Projection'!K7:K42)</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="12">
+      <c r="C16" s="10">
+        <f>SUM(Projection!K7:K42)</f>
+        <v>355101.75000000006</v>
+      </c>
+      <c r="D16" s="10">
         <f>C16*'Profit Split'!$C$7</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="12">
+        <v>177550.87500000003</v>
+      </c>
+      <c r="E16" s="10">
         <f>C16*'Profit Split'!$C$8</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="4" t="s">
+        <v>177550.87500000003</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="24" customHeight="1">
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
     </row>
     <row r="19" spans="2:6" ht="24" customHeight="1">
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="9">
         <v>8000</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="3" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="28" customHeight="1">
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="C20" s="12">
-        <f>MIN('Projection'!L8:L43)</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="4" t="s">
+      <c r="C20" s="10">
+        <f>MIN(Projection!L8:L43)</f>
+        <v>-1019.0357142857147</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="26" customHeight="1">
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="10" t="str">
         <f>IF(B20&lt;-2*'Profit Split'!$C$19,"OVER BUDGET","OK")</f>
-        <v>0</v>
+        <v>OK</v>
       </c>
     </row>
   </sheetData>
@@ -5717,23 +5477,8 @@
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B18:F18"/>
   </mergeCells>
-  <conditionalFormatting sqref="C13:E13">
+  <conditionalFormatting sqref="C13:E16">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C14:E14">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C15:E15">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C16:E16">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
